--- a/Hoadon/HDVao/12/3502550210_HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/12/3502550210_HDDienTuDaCapMa.xlsx
@@ -4799,32 +4799,32 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>C25THM</t>
+          <t>C25TMH</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>8004</t>
+          <t>55561</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>3500636705</t>
+          <t>3500442139</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HOẠ MY</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>114 Lý Thường Kiệt, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/29/42 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
@@ -4838,17 +4838,17 @@
         </is>
       </c>
       <c r="K61" s="13" t="n">
-        <v>5.9563636E7</v>
+        <v>1993333.0</v>
       </c>
       <c r="L61" s="13" t="n">
-        <v>5956364.0</v>
+        <v>159467.0</v>
       </c>
       <c r="M61" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N61" s="13"/>
       <c r="O61" s="13" t="n">
-        <v>6.552E7</v>
+        <v>2152800.0</v>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
@@ -4882,32 +4882,32 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>C25THM</t>
+          <t>C25TMH</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>55657</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>3500636705</t>
+          <t>3500442139</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HOẠ MY</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>114 Lý Thường Kiệt, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/29/42 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
@@ -4921,17 +4921,17 @@
         </is>
       </c>
       <c r="K62" s="13" t="n">
-        <v>2.54634545E8</v>
+        <v>911114.0</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>2.5463455E7</v>
+        <v>72889.0</v>
       </c>
       <c r="M62" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N62" s="13"/>
       <c r="O62" s="13" t="n">
-        <v>2.80098E8</v>
+        <v>984003.0</v>
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
@@ -4965,12 +4965,12 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>C25TYY</t>
+          <t>C25THM</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
@@ -4980,17 +4980,17 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>3500763855</t>
+          <t>3500636705</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN THƯƠNG MẠI DỊCH VỤ HIỀN PHONG</t>
+          <t>CÔNG TY TNHH HOẠ MY</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Số 141 đường Chu Mạnh Trinh, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>114 Lý Thường Kiệt, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
@@ -5004,17 +5004,17 @@
         </is>
       </c>
       <c r="K63" s="13" t="n">
-        <v>3750000.0</v>
+        <v>5.9563636E7</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>300000.0</v>
+        <v>5956364.0</v>
       </c>
       <c r="M63" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N63" s="13"/>
       <c r="O63" s="13" t="n">
-        <v>4050000.0</v>
+        <v>6.552E7</v>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
@@ -5048,32 +5048,32 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>C25TYY</t>
+          <t>C25THM</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>3500763855</t>
+          <t>3500636705</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN THƯƠNG MẠI DỊCH VỤ HIỀN PHONG</t>
+          <t>CÔNG TY TNHH HOẠ MY</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Số 141 đường Chu Mạnh Trinh, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>114 Lý Thường Kiệt, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -5087,17 +5087,17 @@
         </is>
       </c>
       <c r="K64" s="13" t="n">
-        <v>3490741.0</v>
+        <v>2.54634545E8</v>
       </c>
       <c r="L64" s="13" t="n">
-        <v>279259.0</v>
+        <v>2.5463455E7</v>
       </c>
       <c r="M64" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N64" s="13"/>
       <c r="O64" s="13" t="n">
-        <v>3770000.0</v>
+        <v>2.80098E8</v>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
@@ -5131,12 +5131,12 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>C25TDH</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>661</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
@@ -5146,17 +5146,17 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>3500788257</t>
+          <t>3500763855</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ VÀ VẬN TẢI ĐÔNG HÒA PHÁT</t>
+          <t>DOANH NGHIỆP TƯ NHÂN THƯƠNG MẠI DỊCH VỤ HIỀN PHONG</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>158 Phan Chu Trinh, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 141 đường Chu Mạnh Trinh, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -5166,21 +5166,21 @@
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K65" s="13" t="n">
-        <v>2.0105848E7</v>
+        <v>3750000.0</v>
       </c>
       <c r="L65" s="13" t="n">
-        <v>1608468.0</v>
+        <v>300000.0</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>4785417.0</v>
+        <v>0.0</v>
       </c>
       <c r="N65" s="13"/>
       <c r="O65" s="13" t="n">
-        <v>2.1714316E7</v>
+        <v>4050000.0</v>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
@@ -5214,32 +5214,32 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>C25TDH</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>673</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>3500788257</t>
+          <t>3500763855</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ VÀ VẬN TẢI ĐÔNG HÒA PHÁT</t>
+          <t>DOANH NGHIỆP TƯ NHÂN THƯƠNG MẠI DỊCH VỤ HIỀN PHONG</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>158 Phan Chu Trinh, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 141 đường Chu Mạnh Trinh, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
@@ -5249,21 +5249,21 @@
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K66" s="13" t="n">
-        <v>1.6946711E7</v>
+        <v>3490741.0</v>
       </c>
       <c r="L66" s="13" t="n">
-        <v>1355737.0</v>
+        <v>279259.0</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>2953673.0</v>
+        <v>0.0</v>
       </c>
       <c r="N66" s="13"/>
       <c r="O66" s="13" t="n">
-        <v>1.8302448E7</v>
+        <v>3770000.0</v>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
@@ -5302,12 +5302,12 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>07/12/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
@@ -5336,17 +5336,17 @@
         </is>
       </c>
       <c r="K67" s="13" t="n">
-        <v>6683334.0</v>
+        <v>2.0105848E7</v>
       </c>
       <c r="L67" s="13" t="n">
-        <v>534667.0</v>
+        <v>1608468.0</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>430555.0</v>
+        <v>4785417.0</v>
       </c>
       <c r="N67" s="13"/>
       <c r="O67" s="13" t="n">
-        <v>7218001.0</v>
+        <v>2.1714316E7</v>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
@@ -5385,12 +5385,12 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -5419,17 +5419,17 @@
         </is>
       </c>
       <c r="K68" s="13" t="n">
-        <v>2340375.0</v>
+        <v>1.6946711E7</v>
       </c>
       <c r="L68" s="13" t="n">
-        <v>187230.0</v>
+        <v>1355737.0</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>587073.0</v>
+        <v>2953673.0</v>
       </c>
       <c r="N68" s="13"/>
       <c r="O68" s="13" t="n">
-        <v>2527605.0</v>
+        <v>1.8302448E7</v>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
@@ -5468,12 +5468,12 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>07/12/2025</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -5502,17 +5502,17 @@
         </is>
       </c>
       <c r="K69" s="13" t="n">
-        <v>2165130.0</v>
+        <v>6683334.0</v>
       </c>
       <c r="L69" s="13" t="n">
-        <v>173210.0</v>
+        <v>534667.0</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>534870.0</v>
+        <v>430555.0</v>
       </c>
       <c r="N69" s="13"/>
       <c r="O69" s="13" t="n">
-        <v>2338340.0</v>
+        <v>7218001.0</v>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
@@ -5551,12 +5551,12 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -5585,17 +5585,17 @@
         </is>
       </c>
       <c r="K70" s="13" t="n">
-        <v>2.5278078E7</v>
+        <v>2340375.0</v>
       </c>
       <c r="L70" s="13" t="n">
-        <v>2022246.0</v>
+        <v>187230.0</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>6033099.0</v>
+        <v>587073.0</v>
       </c>
       <c r="N70" s="13"/>
       <c r="O70" s="13" t="n">
-        <v>2.7300324E7</v>
+        <v>2527605.0</v>
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -5668,17 +5668,17 @@
         </is>
       </c>
       <c r="K71" s="13" t="n">
-        <v>1.1539153E7</v>
+        <v>2165130.0</v>
       </c>
       <c r="L71" s="13" t="n">
-        <v>923132.0</v>
+        <v>173210.0</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>2726719.0</v>
+        <v>534870.0</v>
       </c>
       <c r="N71" s="13"/>
       <c r="O71" s="13" t="n">
-        <v>1.2462285E7</v>
+        <v>2338340.0</v>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
@@ -5717,12 +5717,12 @@
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
@@ -5751,17 +5751,17 @@
         </is>
       </c>
       <c r="K72" s="13" t="n">
-        <v>6621886.0</v>
+        <v>2.5278078E7</v>
       </c>
       <c r="L72" s="13" t="n">
-        <v>529751.0</v>
+        <v>2022246.0</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>1693606.0</v>
+        <v>6033099.0</v>
       </c>
       <c r="N72" s="13"/>
       <c r="O72" s="13" t="n">
-        <v>7151637.0</v>
+        <v>2.7300324E7</v>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
@@ -5800,12 +5800,12 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>13/12/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -5834,17 +5834,17 @@
         </is>
       </c>
       <c r="K73" s="13" t="n">
-        <v>1.2211436E7</v>
+        <v>1.1539153E7</v>
       </c>
       <c r="L73" s="13" t="n">
-        <v>976915.0</v>
+        <v>923132.0</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>522824.0</v>
+        <v>2726719.0</v>
       </c>
       <c r="N73" s="13"/>
       <c r="O73" s="13" t="n">
-        <v>1.3188351E7</v>
+        <v>1.2462285E7</v>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
@@ -5878,32 +5878,32 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>C25THT</t>
+          <t>C25TDH</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>3500805921</t>
+          <t>3500788257</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI HÙNG TRINH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ VÀ VẬN TẢI ĐÔNG HÒA PHÁT</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>Số 8/18 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>158 Phan Chu Trinh, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
@@ -5913,21 +5913,21 @@
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K74" s="13" t="n">
-        <v>9652222.0</v>
+        <v>6621886.0</v>
       </c>
       <c r="L74" s="13" t="n">
-        <v>772178.0</v>
+        <v>529751.0</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>0.0</v>
+        <v>1693606.0</v>
       </c>
       <c r="N74" s="13"/>
       <c r="O74" s="13" t="n">
-        <v>1.04244E7</v>
+        <v>7151637.0</v>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
@@ -5961,32 +5961,32 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>C25THT</t>
+          <t>C25TDH</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>13/12/2025</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>3500805921</t>
+          <t>3500788257</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI HÙNG TRINH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ VÀ VẬN TẢI ĐÔNG HÒA PHÁT</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>Số 8/18 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>158 Phan Chu Trinh, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr">
@@ -6000,17 +6000,17 @@
         </is>
       </c>
       <c r="K75" s="13" t="n">
-        <v>1.437037E7</v>
+        <v>1.2211436E7</v>
       </c>
       <c r="L75" s="13" t="n">
-        <v>1149630.0</v>
+        <v>976915.0</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>0.0</v>
+        <v>522824.0</v>
       </c>
       <c r="N75" s="13"/>
       <c r="O75" s="13" t="n">
-        <v>1.552E7</v>
+        <v>1.3188351E7</v>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
@@ -6049,12 +6049,12 @@
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -6083,17 +6083,17 @@
         </is>
       </c>
       <c r="K76" s="13" t="n">
-        <v>1.4662037E7</v>
+        <v>9652222.0</v>
       </c>
       <c r="L76" s="13" t="n">
-        <v>1172963.0</v>
+        <v>772178.0</v>
       </c>
       <c r="M76" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N76" s="13"/>
       <c r="O76" s="13" t="n">
-        <v>1.5835E7</v>
+        <v>1.04244E7</v>
       </c>
       <c r="P76" s="7" t="inlineStr">
         <is>
@@ -6132,12 +6132,12 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>15/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
@@ -6162,21 +6162,21 @@
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K77" s="13" t="n">
-        <v>5782222.0</v>
+        <v>1.437037E7</v>
       </c>
       <c r="L77" s="13" t="n">
-        <v>462578.0</v>
+        <v>1149630.0</v>
       </c>
       <c r="M77" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N77" s="13"/>
       <c r="O77" s="13" t="n">
-        <v>6244800.0</v>
+        <v>1.552E7</v>
       </c>
       <c r="P77" s="7" t="inlineStr">
         <is>
@@ -6210,32 +6210,32 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>C25TSV</t>
+          <t>C25THT</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>3500898348</t>
+          <t>3500805921</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ THUẾ SAO VIỆT</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI HÙNG TRINH</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>Số 640 Trương Công Định, Phường Tam Thắng, TP. Hồ Chí Minh, Việt Nam</t>
+          <t>Số 8/18 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
@@ -6249,17 +6249,17 @@
         </is>
       </c>
       <c r="K78" s="13" t="n">
-        <v>1.0E7</v>
+        <v>1.4662037E7</v>
       </c>
       <c r="L78" s="13" t="n">
-        <v>800000.0</v>
+        <v>1172963.0</v>
       </c>
       <c r="M78" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N78" s="13"/>
       <c r="O78" s="13" t="n">
-        <v>1.08E7</v>
+        <v>1.5835E7</v>
       </c>
       <c r="P78" s="7" t="inlineStr">
         <is>
@@ -6293,32 +6293,32 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>C25TSV</t>
+          <t>C25THT</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>3500898348</t>
+          <t>3500805921</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ THUẾ SAO VIỆT</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI HÙNG TRINH</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>Số 640 Trương Công Định, Phường Tam Thắng, TP. Hồ Chí Minh, Việt Nam</t>
+          <t>Số 8/18 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
@@ -6332,17 +6332,17 @@
         </is>
       </c>
       <c r="K79" s="13" t="n">
-        <v>1.0E7</v>
+        <v>5782222.0</v>
       </c>
       <c r="L79" s="13" t="n">
-        <v>800000.0</v>
+        <v>462578.0</v>
       </c>
       <c r="M79" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N79" s="13"/>
       <c r="O79" s="13" t="n">
-        <v>1.08E7</v>
+        <v>6244800.0</v>
       </c>
       <c r="P79" s="7" t="inlineStr">
         <is>
@@ -6376,32 +6376,32 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>C25TBH</t>
+          <t>C25TSV</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>220</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>3501666653</t>
+          <t>3500898348</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI BÁ HUY</t>
+          <t>CÔNG TY TNHH DỊCH VỤ THUẾ SAO VIỆT</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>806/A29 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 640 Trương Công Định, Phường Tam Thắng, TP. Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
@@ -6415,17 +6415,17 @@
         </is>
       </c>
       <c r="K80" s="13" t="n">
-        <v>1666667.0</v>
+        <v>1.0E7</v>
       </c>
       <c r="L80" s="13" t="n">
-        <v>133333.0</v>
+        <v>800000.0</v>
       </c>
       <c r="M80" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N80" s="13"/>
       <c r="O80" s="13" t="n">
-        <v>1800000.0</v>
+        <v>1.08E7</v>
       </c>
       <c r="P80" s="7" t="inlineStr">
         <is>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>C25TAA</t>
+          <t>C25TSV</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -6474,17 +6474,17 @@
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>3501783050</t>
+          <t>3500898348</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN THƯƠNG MẠI SAO ANH</t>
+          <t>CÔNG TY TNHH DỊCH VỤ THUẾ SAO VIỆT</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>Số 669A Nguyễn An Ninh, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 640 Trương Công Định, Phường Tam Thắng, TP. Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
@@ -6498,17 +6498,17 @@
         </is>
       </c>
       <c r="K81" s="13" t="n">
-        <v>5708333.0</v>
+        <v>1.0E7</v>
       </c>
       <c r="L81" s="13" t="n">
-        <v>456667.0</v>
+        <v>800000.0</v>
       </c>
       <c r="M81" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N81" s="13"/>
       <c r="O81" s="13" t="n">
-        <v>6165000.0</v>
+        <v>1.08E7</v>
       </c>
       <c r="P81" s="7" t="inlineStr">
         <is>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>C25TAA</t>
+          <t>C25TBH</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
@@ -6557,17 +6557,17 @@
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>3501783050</t>
+          <t>3501666653</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN THƯƠNG MẠI SAO ANH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI BÁ HUY</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>Số 669A Nguyễn An Ninh, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>806/A29 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr">
@@ -6581,17 +6581,17 @@
         </is>
       </c>
       <c r="K82" s="13" t="n">
-        <v>1.4962963E7</v>
+        <v>1666667.0</v>
       </c>
       <c r="L82" s="13" t="n">
-        <v>1197037.0</v>
+        <v>133333.0</v>
       </c>
       <c r="M82" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N82" s="13"/>
       <c r="O82" s="13" t="n">
-        <v>1.616E7</v>
+        <v>1800000.0</v>
       </c>
       <c r="P82" s="7" t="inlineStr">
         <is>
@@ -6630,12 +6630,12 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
@@ -6664,17 +6664,17 @@
         </is>
       </c>
       <c r="K83" s="13" t="n">
-        <v>1.0757872E7</v>
+        <v>5708333.0</v>
       </c>
       <c r="L83" s="13" t="n">
-        <v>860628.0</v>
+        <v>456667.0</v>
       </c>
       <c r="M83" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N83" s="13"/>
       <c r="O83" s="13" t="n">
-        <v>1.16185E7</v>
+        <v>6165000.0</v>
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
@@ -6713,12 +6713,12 @@
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>15/12/2025</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
@@ -6747,17 +6747,17 @@
         </is>
       </c>
       <c r="K84" s="13" t="n">
-        <v>2.7242223E7</v>
+        <v>1.4962963E7</v>
       </c>
       <c r="L84" s="13" t="n">
-        <v>2179377.0</v>
+        <v>1197037.0</v>
       </c>
       <c r="M84" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N84" s="13"/>
       <c r="O84" s="13" t="n">
-        <v>2.94216E7</v>
+        <v>1.616E7</v>
       </c>
       <c r="P84" s="7" t="inlineStr">
         <is>
@@ -6791,32 +6791,32 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>C25TDL</t>
+          <t>C25TAA</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>107908</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>3501970854</t>
+          <t>3501783050</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+          <t>DOANH NGHIỆP TƯ NHÂN THƯƠNG MẠI SAO ANH</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 669A Nguyễn An Ninh, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
@@ -6830,17 +6830,17 @@
         </is>
       </c>
       <c r="K85" s="13" t="n">
-        <v>3.1054445E7</v>
+        <v>1.0757872E7</v>
       </c>
       <c r="L85" s="13" t="n">
-        <v>2484356.0</v>
+        <v>860628.0</v>
       </c>
       <c r="M85" s="13" t="n">
-        <v>1886837.0</v>
+        <v>0.0</v>
       </c>
       <c r="N85" s="13"/>
       <c r="O85" s="13" t="n">
-        <v>3.3538801E7</v>
+        <v>1.16185E7</v>
       </c>
       <c r="P85" s="7" t="inlineStr">
         <is>
@@ -6874,32 +6874,32 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>C25TDL</t>
+          <t>C25TAA</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>108169</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>3501970854</t>
+          <t>3501783050</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+          <t>DOANH NGHIỆP TƯ NHÂN THƯƠNG MẠI SAO ANH</t>
         </is>
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 669A Nguyễn An Ninh, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
@@ -6913,17 +6913,17 @@
         </is>
       </c>
       <c r="K86" s="13" t="n">
-        <v>8696807.0</v>
+        <v>2.7242223E7</v>
       </c>
       <c r="L86" s="13" t="n">
-        <v>695743.0</v>
+        <v>2179377.0</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>242113.0</v>
+        <v>0.0</v>
       </c>
       <c r="N86" s="13"/>
       <c r="O86" s="13" t="n">
-        <v>9392550.0</v>
+        <v>2.94216E7</v>
       </c>
       <c r="P86" s="7" t="inlineStr">
         <is>
@@ -6962,12 +6962,12 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>108973</t>
+          <t>107908</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>03/12/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
@@ -6996,17 +6996,17 @@
         </is>
       </c>
       <c r="K87" s="13" t="n">
-        <v>4909080.0</v>
+        <v>3.1054445E7</v>
       </c>
       <c r="L87" s="13" t="n">
-        <v>392726.0</v>
+        <v>2484356.0</v>
       </c>
       <c r="M87" s="13" t="n">
-        <v>0.0</v>
+        <v>1886837.0</v>
       </c>
       <c r="N87" s="13"/>
       <c r="O87" s="13" t="n">
-        <v>5301806.0</v>
+        <v>3.3538801E7</v>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
@@ -7045,12 +7045,12 @@
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>108979</t>
+          <t>108169</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>03/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
@@ -7079,17 +7079,17 @@
         </is>
       </c>
       <c r="K88" s="13" t="n">
-        <v>5232408.0</v>
+        <v>8696807.0</v>
       </c>
       <c r="L88" s="13" t="n">
-        <v>418591.0</v>
+        <v>695743.0</v>
       </c>
       <c r="M88" s="13" t="n">
-        <v>52778.0</v>
+        <v>242113.0</v>
       </c>
       <c r="N88" s="13"/>
       <c r="O88" s="13" t="n">
-        <v>5650999.0</v>
+        <v>9392550.0</v>
       </c>
       <c r="P88" s="7" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>108980</t>
+          <t>108973</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
@@ -7162,17 +7162,17 @@
         </is>
       </c>
       <c r="K89" s="13" t="n">
-        <v>1.5349029E7</v>
+        <v>4909080.0</v>
       </c>
       <c r="L89" s="13" t="n">
-        <v>1227922.0</v>
+        <v>392726.0</v>
       </c>
       <c r="M89" s="13" t="n">
-        <v>1669490.0</v>
+        <v>0.0</v>
       </c>
       <c r="N89" s="13"/>
       <c r="O89" s="13" t="n">
-        <v>1.6576951E7</v>
+        <v>5301806.0</v>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
@@ -7211,12 +7211,12 @@
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>112300</t>
+          <t>108979</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>06/12/2025</t>
+          <t>03/12/2025</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
@@ -7245,17 +7245,17 @@
         </is>
       </c>
       <c r="K90" s="13" t="n">
-        <v>6175926.0</v>
+        <v>5232408.0</v>
       </c>
       <c r="L90" s="13" t="n">
-        <v>494074.0</v>
+        <v>418591.0</v>
       </c>
       <c r="M90" s="13" t="n">
-        <v>0.0</v>
+        <v>52778.0</v>
       </c>
       <c r="N90" s="13"/>
       <c r="O90" s="13" t="n">
-        <v>6670000.0</v>
+        <v>5650999.0</v>
       </c>
       <c r="P90" s="7" t="inlineStr">
         <is>
@@ -7294,12 +7294,12 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>112649</t>
+          <t>108980</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>03/12/2025</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
@@ -7328,17 +7328,17 @@
         </is>
       </c>
       <c r="K91" s="13" t="n">
-        <v>0.0</v>
+        <v>1.5349029E7</v>
       </c>
       <c r="L91" s="13" t="n">
-        <v>0.0</v>
+        <v>1227922.0</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>0.0</v>
+        <v>1669490.0</v>
       </c>
       <c r="N91" s="13"/>
       <c r="O91" s="13" t="n">
-        <v>0.0</v>
+        <v>1.6576951E7</v>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>114095</t>
+          <t>112300</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>06/12/2025</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
@@ -7411,17 +7411,17 @@
         </is>
       </c>
       <c r="K92" s="13" t="n">
-        <v>7154210.0</v>
+        <v>6175926.0</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>572337.0</v>
+        <v>494074.0</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>177178.0</v>
+        <v>0.0</v>
       </c>
       <c r="N92" s="13"/>
       <c r="O92" s="13" t="n">
-        <v>7726547.0</v>
+        <v>6670000.0</v>
       </c>
       <c r="P92" s="7" t="inlineStr">
         <is>
@@ -7460,12 +7460,12 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>114679</t>
+          <t>112649</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
@@ -7494,17 +7494,17 @@
         </is>
       </c>
       <c r="K93" s="13" t="n">
-        <v>6457778.0</v>
+        <v>0.0</v>
       </c>
       <c r="L93" s="13" t="n">
-        <v>516622.0</v>
+        <v>0.0</v>
       </c>
       <c r="M93" s="13" t="n">
-        <v>542222.0</v>
+        <v>0.0</v>
       </c>
       <c r="N93" s="13"/>
       <c r="O93" s="13" t="n">
-        <v>6974400.0</v>
+        <v>0.0</v>
       </c>
       <c r="P93" s="7" t="inlineStr">
         <is>
@@ -7543,12 +7543,12 @@
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>116050</t>
+          <t>114095</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
@@ -7577,17 +7577,17 @@
         </is>
       </c>
       <c r="K94" s="13" t="n">
-        <v>5130556.0</v>
+        <v>7154210.0</v>
       </c>
       <c r="L94" s="13" t="n">
-        <v>410444.0</v>
+        <v>572337.0</v>
       </c>
       <c r="M94" s="13" t="n">
-        <v>332407.0</v>
+        <v>177178.0</v>
       </c>
       <c r="N94" s="13"/>
       <c r="O94" s="13" t="n">
-        <v>5541000.0</v>
+        <v>7726547.0</v>
       </c>
       <c r="P94" s="7" t="inlineStr">
         <is>
@@ -7626,12 +7626,12 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>116514</t>
+          <t>114679</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
@@ -7660,17 +7660,17 @@
         </is>
       </c>
       <c r="K95" s="13" t="n">
-        <v>1.93056E7</v>
+        <v>6457778.0</v>
       </c>
       <c r="L95" s="13" t="n">
-        <v>1544448.0</v>
+        <v>516622.0</v>
       </c>
       <c r="M95" s="13" t="n">
-        <v>0.0</v>
+        <v>542222.0</v>
       </c>
       <c r="N95" s="13"/>
       <c r="O95" s="13" t="n">
-        <v>2.0850048E7</v>
+        <v>6974400.0</v>
       </c>
       <c r="P95" s="7" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>117285</t>
+          <t>116050</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
@@ -7743,17 +7743,17 @@
         </is>
       </c>
       <c r="K96" s="13" t="n">
-        <v>1606481.0</v>
+        <v>5130556.0</v>
       </c>
       <c r="L96" s="13" t="n">
-        <v>128519.0</v>
+        <v>410444.0</v>
       </c>
       <c r="M96" s="13" t="n">
-        <v>120370.0</v>
+        <v>332407.0</v>
       </c>
       <c r="N96" s="13"/>
       <c r="O96" s="13" t="n">
-        <v>1735000.0</v>
+        <v>5541000.0</v>
       </c>
       <c r="P96" s="7" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>117287</t>
+          <t>116514</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -7826,17 +7826,17 @@
         </is>
       </c>
       <c r="K97" s="13" t="n">
-        <v>1944445.0</v>
+        <v>1.93056E7</v>
       </c>
       <c r="L97" s="13" t="n">
-        <v>155556.0</v>
+        <v>1544448.0</v>
       </c>
       <c r="M97" s="13" t="n">
-        <v>69445.0</v>
+        <v>0.0</v>
       </c>
       <c r="N97" s="13"/>
       <c r="O97" s="13" t="n">
-        <v>2100001.0</v>
+        <v>2.0850048E7</v>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
@@ -7875,12 +7875,12 @@
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>119122</t>
+          <t>117285</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>13/12/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
@@ -7909,17 +7909,17 @@
         </is>
       </c>
       <c r="K98" s="13" t="n">
-        <v>7722240.0</v>
+        <v>1606481.0</v>
       </c>
       <c r="L98" s="13" t="n">
-        <v>617779.0</v>
+        <v>128519.0</v>
       </c>
       <c r="M98" s="13" t="n">
-        <v>0.0</v>
+        <v>120370.0</v>
       </c>
       <c r="N98" s="13"/>
       <c r="O98" s="13" t="n">
-        <v>8340019.0</v>
+        <v>1735000.0</v>
       </c>
       <c r="P98" s="7" t="inlineStr">
         <is>
@@ -7958,12 +7958,12 @@
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>119607</t>
+          <t>117287</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>13/12/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
@@ -7992,17 +7992,17 @@
         </is>
       </c>
       <c r="K99" s="13" t="n">
-        <v>1584000.0</v>
+        <v>1944445.0</v>
       </c>
       <c r="L99" s="13" t="n">
-        <v>126720.0</v>
+        <v>155556.0</v>
       </c>
       <c r="M99" s="13" t="n">
-        <v>0.0</v>
+        <v>69445.0</v>
       </c>
       <c r="N99" s="13"/>
       <c r="O99" s="13" t="n">
-        <v>1710720.0</v>
+        <v>2100001.0</v>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>119608</t>
+          <t>119122</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
@@ -8075,17 +8075,17 @@
         </is>
       </c>
       <c r="K100" s="13" t="n">
-        <v>541308.0</v>
+        <v>7722240.0</v>
       </c>
       <c r="L100" s="13" t="n">
-        <v>43305.0</v>
+        <v>617779.0</v>
       </c>
       <c r="M100" s="13" t="n">
-        <v>10692.0</v>
+        <v>0.0</v>
       </c>
       <c r="N100" s="13"/>
       <c r="O100" s="13" t="n">
-        <v>584613.0</v>
+        <v>8340019.0</v>
       </c>
       <c r="P100" s="7" t="inlineStr">
         <is>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>121180</t>
+          <t>119607</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>15/12/2025</t>
+          <t>13/12/2025</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
@@ -8158,17 +8158,17 @@
         </is>
       </c>
       <c r="K101" s="13" t="n">
-        <v>1.1258352E7</v>
+        <v>1584000.0</v>
       </c>
       <c r="L101" s="13" t="n">
-        <v>900668.0</v>
+        <v>126720.0</v>
       </c>
       <c r="M101" s="13" t="n">
-        <v>175926.0</v>
+        <v>0.0</v>
       </c>
       <c r="N101" s="13"/>
       <c r="O101" s="13" t="n">
-        <v>1.215902E7</v>
+        <v>1710720.0</v>
       </c>
       <c r="P101" s="7" t="inlineStr">
         <is>
@@ -8202,32 +8202,32 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>C25TTP</t>
+          <t>C25TDL</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>119608</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>13/12/2025</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>3501981599</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI THỊNH PHÁT VN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>Số 138 Nguyễn Thiện Thuật, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I102" s="7" t="inlineStr">
@@ -8237,21 +8237,21 @@
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>Công ty TNHH Thạnh Hương Bến Đình</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K102" s="13" t="n">
-        <v>5000000.0</v>
+        <v>541308.0</v>
       </c>
       <c r="L102" s="13" t="n">
-        <v>500000.0</v>
+        <v>43305.0</v>
       </c>
       <c r="M102" s="13" t="n">
-        <v>0.0</v>
+        <v>10692.0</v>
       </c>
       <c r="N102" s="13"/>
       <c r="O102" s="13" t="n">
-        <v>5500000.0</v>
+        <v>584613.0</v>
       </c>
       <c r="P102" s="7" t="inlineStr">
         <is>
@@ -8285,32 +8285,32 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>C25THH</t>
+          <t>C25TDL</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>121180</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>3502203697</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HIỀN HÙNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>số 30 Phan Đăng Lưu, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I103" s="7" t="inlineStr">
@@ -8324,17 +8324,17 @@
         </is>
       </c>
       <c r="K103" s="13" t="n">
-        <v>1833333.0</v>
+        <v>1.1258352E7</v>
       </c>
       <c r="L103" s="13" t="n">
-        <v>146667.0</v>
+        <v>900668.0</v>
       </c>
       <c r="M103" s="13" t="n">
-        <v>0.0</v>
+        <v>175926.0</v>
       </c>
       <c r="N103" s="13"/>
       <c r="O103" s="13" t="n">
-        <v>1980000.0</v>
+        <v>1.215902E7</v>
       </c>
       <c r="P103" s="7" t="inlineStr">
         <is>
@@ -8368,32 +8368,32 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>C25TPQ</t>
+          <t>C25TDL</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>122472</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>3502236614</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN QUỐC ĐẠI - PHÚ QUÝ</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H104" s="6" t="inlineStr">
         <is>
-          <t>Số 140/8/5A Lưu Chí Hiếu, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I104" s="7" t="inlineStr">
@@ -8407,17 +8407,17 @@
         </is>
       </c>
       <c r="K104" s="13" t="n">
-        <v>1.1299074E7</v>
+        <v>2083333.0</v>
       </c>
       <c r="L104" s="13" t="n">
-        <v>903926.0</v>
+        <v>166667.0</v>
       </c>
       <c r="M104" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N104" s="13"/>
       <c r="O104" s="13" t="n">
-        <v>1.2203E7</v>
+        <v>2250000.0</v>
       </c>
       <c r="P104" s="7" t="inlineStr">
         <is>
@@ -8451,32 +8451,32 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>C25TMG</t>
+          <t>C25TDL</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>19464</t>
+          <t>122565</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>3502243033</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I105" s="7" t="inlineStr">
@@ -8490,17 +8490,17 @@
         </is>
       </c>
       <c r="K105" s="13" t="n">
-        <v>7592593.0</v>
+        <v>7618166.0</v>
       </c>
       <c r="L105" s="13" t="n">
-        <v>607407.0</v>
+        <v>609454.0</v>
       </c>
       <c r="M105" s="13" t="n">
-        <v>0.0</v>
+        <v>565167.0</v>
       </c>
       <c r="N105" s="13"/>
       <c r="O105" s="13" t="n">
-        <v>8200000.0</v>
+        <v>8227620.0</v>
       </c>
       <c r="P105" s="7" t="inlineStr">
         <is>
@@ -8534,32 +8534,32 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>C25TMG</t>
+          <t>C25TDL</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>19546</t>
+          <t>122707</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>3502243033</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I106" s="7" t="inlineStr">
@@ -8573,17 +8573,17 @@
         </is>
       </c>
       <c r="K106" s="13" t="n">
-        <v>4333333.0</v>
+        <v>3850019.0</v>
       </c>
       <c r="L106" s="13" t="n">
-        <v>346667.0</v>
+        <v>308003.0</v>
       </c>
       <c r="M106" s="13" t="n">
-        <v>0.0</v>
+        <v>38889.0</v>
       </c>
       <c r="N106" s="13"/>
       <c r="O106" s="13" t="n">
-        <v>4680000.0</v>
+        <v>4158022.0</v>
       </c>
       <c r="P106" s="7" t="inlineStr">
         <is>
@@ -8617,32 +8617,32 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>C25TMG</t>
+          <t>C25TTP</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>19634</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>03/12/2025</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>3502243033</t>
+          <t>3501981599</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI THỊNH PHÁT VN</t>
         </is>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 138 Nguyễn Thiện Thuật, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I107" s="7" t="inlineStr">
@@ -8652,21 +8652,21 @@
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
       <c r="K107" s="13" t="n">
-        <v>3194444.0</v>
+        <v>5000000.0</v>
       </c>
       <c r="L107" s="13" t="n">
-        <v>255556.0</v>
+        <v>500000.0</v>
       </c>
       <c r="M107" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N107" s="13"/>
       <c r="O107" s="13" t="n">
-        <v>3450000.0</v>
+        <v>5500000.0</v>
       </c>
       <c r="P107" s="7" t="inlineStr">
         <is>
@@ -8700,32 +8700,32 @@
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>C25TMG</t>
+          <t>C25TTP</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>19888</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>3502243033</t>
+          <t>3501981599</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI THỊNH PHÁT VN</t>
         </is>
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
-          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 138 Nguyễn Thiện Thuật, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I108" s="7" t="inlineStr">
@@ -8735,21 +8735,21 @@
       </c>
       <c r="J108" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
       <c r="K108" s="13" t="n">
-        <v>8610185.0</v>
+        <v>1.0772727E7</v>
       </c>
       <c r="L108" s="13" t="n">
-        <v>688815.0</v>
+        <v>1077273.0</v>
       </c>
       <c r="M108" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N108" s="13"/>
       <c r="O108" s="13" t="n">
-        <v>9299000.0</v>
+        <v>1.185E7</v>
       </c>
       <c r="P108" s="7" t="inlineStr">
         <is>
@@ -8783,12 +8783,12 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>C25TMG</t>
+          <t>C25THH</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>19889</t>
+          <t>229</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
@@ -8798,17 +8798,17 @@
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>3502243033</t>
+          <t>3502203697</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HIỀN HÙNG</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>số 30 Phan Đăng Lưu, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I109" s="7" t="inlineStr">
@@ -8822,17 +8822,17 @@
         </is>
       </c>
       <c r="K109" s="13" t="n">
-        <v>1453704.0</v>
+        <v>1833333.0</v>
       </c>
       <c r="L109" s="13" t="n">
-        <v>116296.0</v>
+        <v>146667.0</v>
       </c>
       <c r="M109" s="13" t="n">
-        <v>178296.0</v>
+        <v>0.0</v>
       </c>
       <c r="N109" s="13"/>
       <c r="O109" s="13" t="n">
-        <v>1570000.0</v>
+        <v>1980000.0</v>
       </c>
       <c r="P109" s="7" t="inlineStr">
         <is>
@@ -8866,32 +8866,32 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>C25TMG</t>
+          <t>C25TPQ</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>20215</t>
+          <t>930</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>06/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>3502243033</t>
+          <t>3502236614</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
+          <t>DOANH NGHIỆP TƯ NHÂN QUỐC ĐẠI - PHÚ QUÝ</t>
         </is>
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
-          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 140/8/5A Lưu Chí Hiếu, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I110" s="7" t="inlineStr">
@@ -8905,17 +8905,17 @@
         </is>
       </c>
       <c r="K110" s="13" t="n">
-        <v>5324074.0</v>
+        <v>1.1299074E7</v>
       </c>
       <c r="L110" s="13" t="n">
-        <v>425926.0</v>
+        <v>903926.0</v>
       </c>
       <c r="M110" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N110" s="13"/>
       <c r="O110" s="13" t="n">
-        <v>5750000.0</v>
+        <v>1.2203E7</v>
       </c>
       <c r="P110" s="7" t="inlineStr">
         <is>
@@ -8954,12 +8954,12 @@
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>20300</t>
+          <t>19464</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
@@ -8988,17 +8988,17 @@
         </is>
       </c>
       <c r="K111" s="13" t="n">
-        <v>71296.0</v>
+        <v>7592593.0</v>
       </c>
       <c r="L111" s="13" t="n">
-        <v>5704.0</v>
+        <v>607407.0</v>
       </c>
       <c r="M111" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N111" s="13"/>
       <c r="O111" s="13" t="n">
-        <v>77000.0</v>
+        <v>8200000.0</v>
       </c>
       <c r="P111" s="7" t="inlineStr">
         <is>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>20301</t>
+          <t>19546</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
@@ -9071,17 +9071,17 @@
         </is>
       </c>
       <c r="K112" s="13" t="n">
-        <v>8084259.0</v>
+        <v>4333333.0</v>
       </c>
       <c r="L112" s="13" t="n">
-        <v>646741.0</v>
+        <v>346667.0</v>
       </c>
       <c r="M112" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N112" s="13"/>
       <c r="O112" s="13" t="n">
-        <v>8731000.0</v>
+        <v>4680000.0</v>
       </c>
       <c r="P112" s="7" t="inlineStr">
         <is>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>20760</t>
+          <t>19634</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>03/12/2025</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
@@ -9154,17 +9154,17 @@
         </is>
       </c>
       <c r="K113" s="13" t="n">
-        <v>532407.0</v>
+        <v>3194444.0</v>
       </c>
       <c r="L113" s="13" t="n">
-        <v>42593.0</v>
+        <v>255556.0</v>
       </c>
       <c r="M113" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N113" s="13"/>
       <c r="O113" s="13" t="n">
-        <v>575000.0</v>
+        <v>3450000.0</v>
       </c>
       <c r="P113" s="7" t="inlineStr">
         <is>
@@ -9203,12 +9203,12 @@
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>20762</t>
+          <t>19888</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
@@ -9237,17 +9237,17 @@
         </is>
       </c>
       <c r="K114" s="13" t="n">
-        <v>5324074.0</v>
+        <v>8610185.0</v>
       </c>
       <c r="L114" s="13" t="n">
-        <v>425926.0</v>
+        <v>688815.0</v>
       </c>
       <c r="M114" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N114" s="13"/>
       <c r="O114" s="13" t="n">
-        <v>5750000.0</v>
+        <v>9299000.0</v>
       </c>
       <c r="P114" s="7" t="inlineStr">
         <is>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>20982</t>
+          <t>19889</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
@@ -9320,17 +9320,17 @@
         </is>
       </c>
       <c r="K115" s="13" t="n">
-        <v>9175926.0</v>
+        <v>1453704.0</v>
       </c>
       <c r="L115" s="13" t="n">
-        <v>734074.0</v>
+        <v>116296.0</v>
       </c>
       <c r="M115" s="13" t="n">
-        <v>1134474.0</v>
+        <v>178296.0</v>
       </c>
       <c r="N115" s="13"/>
       <c r="O115" s="13" t="n">
-        <v>9910000.0</v>
+        <v>1570000.0</v>
       </c>
       <c r="P115" s="7" t="inlineStr">
         <is>
@@ -9369,12 +9369,12 @@
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>21382</t>
+          <t>20215</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>13/12/2025</t>
+          <t>06/12/2025</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
@@ -9403,17 +9403,17 @@
         </is>
       </c>
       <c r="K116" s="13" t="n">
-        <v>2472222.0</v>
+        <v>5324074.0</v>
       </c>
       <c r="L116" s="13" t="n">
-        <v>197778.0</v>
+        <v>425926.0</v>
       </c>
       <c r="M116" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N116" s="13"/>
       <c r="O116" s="13" t="n">
-        <v>2670000.0</v>
+        <v>5750000.0</v>
       </c>
       <c r="P116" s="7" t="inlineStr">
         <is>
@@ -9452,12 +9452,12 @@
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>21384</t>
+          <t>20300</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>13/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
@@ -9486,17 +9486,17 @@
         </is>
       </c>
       <c r="K117" s="13" t="n">
-        <v>2.4305556E7</v>
+        <v>71296.0</v>
       </c>
       <c r="L117" s="13" t="n">
-        <v>1944444.0</v>
+        <v>5704.0</v>
       </c>
       <c r="M117" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N117" s="13"/>
       <c r="O117" s="13" t="n">
-        <v>2.625E7</v>
+        <v>77000.0</v>
       </c>
       <c r="P117" s="7" t="inlineStr">
         <is>
@@ -9535,12 +9535,12 @@
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>21439</t>
+          <t>20301</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>15/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
@@ -9569,17 +9569,17 @@
         </is>
       </c>
       <c r="K118" s="13" t="n">
-        <v>7285185.0</v>
+        <v>8084259.0</v>
       </c>
       <c r="L118" s="13" t="n">
-        <v>582815.0</v>
+        <v>646741.0</v>
       </c>
       <c r="M118" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N118" s="13"/>
       <c r="O118" s="13" t="n">
-        <v>7868000.0</v>
+        <v>8731000.0</v>
       </c>
       <c r="P118" s="7" t="inlineStr">
         <is>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>21441</t>
+          <t>20760</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>15/12/2025</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
@@ -9652,17 +9652,17 @@
         </is>
       </c>
       <c r="K119" s="13" t="n">
-        <v>1.3884259E7</v>
+        <v>532407.0</v>
       </c>
       <c r="L119" s="13" t="n">
-        <v>1110741.0</v>
+        <v>42593.0</v>
       </c>
       <c r="M119" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N119" s="13"/>
       <c r="O119" s="13" t="n">
-        <v>1.4995E7</v>
+        <v>575000.0</v>
       </c>
       <c r="P119" s="7" t="inlineStr">
         <is>
@@ -9696,32 +9696,32 @@
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>C25TTL</t>
+          <t>C25TMG</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>20762</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>3502250601</t>
+          <t>3502243033</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ THẢO LÊ</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
         </is>
       </c>
       <c r="H120" s="6" t="inlineStr">
         <is>
-          <t>Số 15 Nguyễn Kim, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I120" s="7" t="inlineStr">
@@ -9735,17 +9735,17 @@
         </is>
       </c>
       <c r="K120" s="13" t="n">
-        <v>4498443.0</v>
+        <v>5324074.0</v>
       </c>
       <c r="L120" s="13" t="n">
-        <v>359875.0</v>
+        <v>425926.0</v>
       </c>
       <c r="M120" s="13" t="n">
-        <v>1760925.0</v>
+        <v>0.0</v>
       </c>
       <c r="N120" s="13"/>
       <c r="O120" s="13" t="n">
-        <v>4858318.0</v>
+        <v>5750000.0</v>
       </c>
       <c r="P120" s="7" t="inlineStr">
         <is>
@@ -9779,32 +9779,32 @@
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>C25TTT</t>
+          <t>C25TMG</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>12534</t>
+          <t>20982</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>3502252817</t>
+          <t>3502243033</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I121" s="7" t="inlineStr">
@@ -9814,21 +9814,21 @@
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K121" s="13" t="n">
-        <v>2.962037E7</v>
+        <v>9175926.0</v>
       </c>
       <c r="L121" s="13" t="n">
-        <v>2369630.0</v>
+        <v>734074.0</v>
       </c>
       <c r="M121" s="13" t="n">
-        <v>0.0</v>
+        <v>1134474.0</v>
       </c>
       <c r="N121" s="13"/>
       <c r="O121" s="13" t="n">
-        <v>3.199E7</v>
+        <v>9910000.0</v>
       </c>
       <c r="P121" s="7" t="inlineStr">
         <is>
@@ -9862,32 +9862,32 @@
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>C25TTT</t>
+          <t>C25TMG</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>21382</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>06/12/2025</t>
+          <t>13/12/2025</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>3502252817</t>
+          <t>3502243033</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
         </is>
       </c>
       <c r="H122" s="6" t="inlineStr">
         <is>
-          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I122" s="7" t="inlineStr">
@@ -9897,21 +9897,21 @@
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K122" s="13" t="n">
-        <v>2.0324073E7</v>
+        <v>2472222.0</v>
       </c>
       <c r="L122" s="13" t="n">
-        <v>1625927.0</v>
+        <v>197778.0</v>
       </c>
       <c r="M122" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N122" s="13"/>
       <c r="O122" s="13" t="n">
-        <v>2.195E7</v>
+        <v>2670000.0</v>
       </c>
       <c r="P122" s="7" t="inlineStr">
         <is>
@@ -9945,32 +9945,32 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>C25TTT</t>
+          <t>C25TMG</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>21384</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>13/12/2025</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>3502252817</t>
+          <t>3502243033</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
         </is>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I123" s="7" t="inlineStr">
@@ -9980,21 +9980,21 @@
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K123" s="13" t="n">
-        <v>1.9667592E7</v>
+        <v>2.4305556E7</v>
       </c>
       <c r="L123" s="13" t="n">
-        <v>1573408.0</v>
+        <v>1944444.0</v>
       </c>
       <c r="M123" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N123" s="13"/>
       <c r="O123" s="13" t="n">
-        <v>2.1241E7</v>
+        <v>2.625E7</v>
       </c>
       <c r="P123" s="7" t="inlineStr">
         <is>
@@ -10028,32 +10028,32 @@
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>C25TTT</t>
+          <t>C25TMG</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>12827</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>3502252817</t>
+          <t>3502243033</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
         </is>
       </c>
       <c r="H124" s="6" t="inlineStr">
         <is>
-          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I124" s="7" t="inlineStr">
@@ -10063,21 +10063,21 @@
       </c>
       <c r="J124" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K124" s="13" t="n">
-        <v>1.8182408E7</v>
+        <v>7285185.0</v>
       </c>
       <c r="L124" s="13" t="n">
-        <v>1454592.0</v>
+        <v>582815.0</v>
       </c>
       <c r="M124" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N124" s="13"/>
       <c r="O124" s="13" t="n">
-        <v>1.9637E7</v>
+        <v>7868000.0</v>
       </c>
       <c r="P124" s="7" t="inlineStr">
         <is>
@@ -10111,32 +10111,32 @@
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>C25TTT</t>
+          <t>C25TMG</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>13295</t>
+          <t>21441</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>3502252817</t>
+          <t>3502243033</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I125" s="7" t="inlineStr">
@@ -10146,21 +10146,21 @@
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K125" s="13" t="n">
-        <v>3.7936111E7</v>
+        <v>1.3884259E7</v>
       </c>
       <c r="L125" s="13" t="n">
-        <v>3034889.0</v>
+        <v>1110741.0</v>
       </c>
       <c r="M125" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N125" s="13"/>
       <c r="O125" s="13" t="n">
-        <v>4.0971E7</v>
+        <v>1.4995E7</v>
       </c>
       <c r="P125" s="7" t="inlineStr">
         <is>
@@ -10194,32 +10194,32 @@
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TTL</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>3502343006</t>
+          <t>3502250601</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ THẢO LÊ</t>
         </is>
       </c>
       <c r="H126" s="6" t="inlineStr">
         <is>
-          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 15 Nguyễn Kim, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I126" s="7" t="inlineStr">
@@ -10233,17 +10233,17 @@
         </is>
       </c>
       <c r="K126" s="13" t="n">
-        <v>2997825.0</v>
+        <v>4498443.0</v>
       </c>
       <c r="L126" s="13" t="n">
-        <v>239826.0</v>
+        <v>359875.0</v>
       </c>
       <c r="M126" s="13" t="n">
-        <v>529027.0</v>
+        <v>1760925.0</v>
       </c>
       <c r="N126" s="13"/>
       <c r="O126" s="13" t="n">
-        <v>3237651.0</v>
+        <v>4858318.0</v>
       </c>
       <c r="P126" s="7" t="inlineStr">
         <is>
@@ -10277,32 +10277,32 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TTT</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>12534</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>3502343006</t>
+          <t>3502252817</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
         </is>
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I127" s="7" t="inlineStr">
@@ -10312,21 +10312,21 @@
       </c>
       <c r="J127" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K127" s="13" t="n">
-        <v>8651269.0</v>
+        <v>2.962037E7</v>
       </c>
       <c r="L127" s="13" t="n">
-        <v>692101.0</v>
+        <v>2369630.0</v>
       </c>
       <c r="M127" s="13" t="n">
-        <v>1526688.0</v>
+        <v>0.0</v>
       </c>
       <c r="N127" s="13"/>
       <c r="O127" s="13" t="n">
-        <v>9343370.0</v>
+        <v>3.199E7</v>
       </c>
       <c r="P127" s="7" t="inlineStr">
         <is>
@@ -10360,32 +10360,32 @@
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TTT</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>12654</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>06/12/2025</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>3502343006</t>
+          <t>3502252817</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
         </is>
       </c>
       <c r="H128" s="6" t="inlineStr">
         <is>
-          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I128" s="7" t="inlineStr">
@@ -10395,21 +10395,21 @@
       </c>
       <c r="J128" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K128" s="13" t="n">
-        <v>2267533.0</v>
+        <v>2.0324073E7</v>
       </c>
       <c r="L128" s="13" t="n">
-        <v>181403.0</v>
+        <v>1625927.0</v>
       </c>
       <c r="M128" s="13" t="n">
-        <v>369143.0</v>
+        <v>0.0</v>
       </c>
       <c r="N128" s="13"/>
       <c r="O128" s="13" t="n">
-        <v>2448936.0</v>
+        <v>2.195E7</v>
       </c>
       <c r="P128" s="7" t="inlineStr">
         <is>
@@ -10443,32 +10443,32 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TTT</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>03/12/2025</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>3502343006</t>
+          <t>3502252817</t>
         </is>
       </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
         <is>
-          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I129" s="7" t="inlineStr">
@@ -10478,21 +10478,21 @@
       </c>
       <c r="J129" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K129" s="13" t="n">
-        <v>822222.0</v>
+        <v>1.9667592E7</v>
       </c>
       <c r="L129" s="13" t="n">
-        <v>65778.0</v>
+        <v>1573408.0</v>
       </c>
       <c r="M129" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N129" s="13"/>
       <c r="O129" s="13" t="n">
-        <v>888000.0</v>
+        <v>2.1241E7</v>
       </c>
       <c r="P129" s="7" t="inlineStr">
         <is>
@@ -10526,32 +10526,32 @@
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TTT</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>12827</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>3502343006</t>
+          <t>3502252817</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
         </is>
       </c>
       <c r="H130" s="6" t="inlineStr">
         <is>
-          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I130" s="7" t="inlineStr">
@@ -10561,21 +10561,21 @@
       </c>
       <c r="J130" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K130" s="13" t="n">
-        <v>1644444.0</v>
+        <v>1.8182408E7</v>
       </c>
       <c r="L130" s="13" t="n">
-        <v>131556.0</v>
+        <v>1454592.0</v>
       </c>
       <c r="M130" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N130" s="13"/>
       <c r="O130" s="13" t="n">
-        <v>1776000.0</v>
+        <v>1.9637E7</v>
       </c>
       <c r="P130" s="7" t="inlineStr">
         <is>
@@ -10609,32 +10609,32 @@
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TTT</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>13295</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>3502343006</t>
+          <t>3502252817</t>
         </is>
       </c>
       <c r="G131" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
         <is>
-          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I131" s="7" t="inlineStr">
@@ -10644,21 +10644,21 @@
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K131" s="13" t="n">
-        <v>1444800.0</v>
+        <v>3.7936111E7</v>
       </c>
       <c r="L131" s="13" t="n">
-        <v>115584.0</v>
+        <v>3034889.0</v>
       </c>
       <c r="M131" s="13" t="n">
-        <v>235200.0</v>
+        <v>0.0</v>
       </c>
       <c r="N131" s="13"/>
       <c r="O131" s="13" t="n">
-        <v>1560384.0</v>
+        <v>4.0971E7</v>
       </c>
       <c r="P131" s="7" t="inlineStr">
         <is>
@@ -10697,12 +10697,12 @@
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
@@ -10731,17 +10731,17 @@
         </is>
       </c>
       <c r="K132" s="13" t="n">
-        <v>6626740.0</v>
+        <v>2997825.0</v>
       </c>
       <c r="L132" s="13" t="n">
-        <v>530140.0</v>
+        <v>239826.0</v>
       </c>
       <c r="M132" s="13" t="n">
-        <v>1254924.0</v>
+        <v>529027.0</v>
       </c>
       <c r="N132" s="13"/>
       <c r="O132" s="13" t="n">
-        <v>7156880.0</v>
+        <v>3237651.0</v>
       </c>
       <c r="P132" s="7" t="inlineStr">
         <is>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
@@ -10814,17 +10814,17 @@
         </is>
       </c>
       <c r="K133" s="13" t="n">
-        <v>592592.0</v>
+        <v>8651269.0</v>
       </c>
       <c r="L133" s="13" t="n">
-        <v>47407.0</v>
+        <v>692101.0</v>
       </c>
       <c r="M133" s="13" t="n">
-        <v>0.0</v>
+        <v>1526688.0</v>
       </c>
       <c r="N133" s="13"/>
       <c r="O133" s="13" t="n">
-        <v>639999.0</v>
+        <v>9343370.0</v>
       </c>
       <c r="P133" s="7" t="inlineStr">
         <is>
@@ -10858,32 +10858,32 @@
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>C25TMP</t>
+          <t>C25THP</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>3502356929</t>
+          <t>3502343006</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VẬN TẢI TÂM MINH PHÁT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
         </is>
       </c>
       <c r="H134" s="6" t="inlineStr">
         <is>
-          <t>Số 1621 Quốc lộ 55, Khu phố Long An, Xã Long Điền, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I134" s="7" t="inlineStr">
@@ -10897,15 +10897,17 @@
         </is>
       </c>
       <c r="K134" s="13" t="n">
-        <v>1.53055556E8</v>
+        <v>2267533.0</v>
       </c>
       <c r="L134" s="13" t="n">
-        <v>1.2244444E7</v>
-      </c>
-      <c r="M134" s="13"/>
+        <v>181403.0</v>
+      </c>
+      <c r="M134" s="13" t="n">
+        <v>369143.0</v>
+      </c>
       <c r="N134" s="13"/>
       <c r="O134" s="13" t="n">
-        <v>1.653E8</v>
+        <v>2448936.0</v>
       </c>
       <c r="P134" s="7" t="inlineStr">
         <is>
@@ -10939,32 +10941,32 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>C25TVT</t>
+          <t>C25THP</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>03/12/2025</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>3502358700</t>
+          <t>3502343006</t>
         </is>
       </c>
       <c r="G135" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ IT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
         <is>
-          <t>533 Nguyễn An Ninh, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I135" s="7" t="inlineStr">
@@ -10978,15 +10980,17 @@
         </is>
       </c>
       <c r="K135" s="13" t="n">
-        <v>1650000.0</v>
+        <v>822222.0</v>
       </c>
       <c r="L135" s="13" t="n">
-        <v>132000.0</v>
-      </c>
-      <c r="M135" s="13"/>
+        <v>65778.0</v>
+      </c>
+      <c r="M135" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N135" s="13"/>
       <c r="O135" s="13" t="n">
-        <v>1782000.0</v>
+        <v>888000.0</v>
       </c>
       <c r="P135" s="7" t="inlineStr">
         <is>
@@ -11020,32 +11024,32 @@
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>C25TVT</t>
+          <t>C25THP</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>3502358700</t>
+          <t>3502343006</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ IT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
         </is>
       </c>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>533 Nguyễn An Ninh, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I136" s="7" t="inlineStr">
@@ -11059,15 +11063,17 @@
         </is>
       </c>
       <c r="K136" s="13" t="n">
-        <v>900000.0</v>
+        <v>1644444.0</v>
       </c>
       <c r="L136" s="13" t="n">
-        <v>72000.0</v>
-      </c>
-      <c r="M136" s="13"/>
+        <v>131556.0</v>
+      </c>
+      <c r="M136" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N136" s="13"/>
       <c r="O136" s="13" t="n">
-        <v>972000.0</v>
+        <v>1776000.0</v>
       </c>
       <c r="P136" s="7" t="inlineStr">
         <is>
@@ -11101,32 +11107,32 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>C25TLP</t>
+          <t>C25THP</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>03/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>3502376562</t>
+          <t>3502343006</t>
         </is>
       </c>
       <c r="G137" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THỰC PHẨM HƯNG LỘC PHÁT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
         </is>
       </c>
       <c r="H137" s="6" t="inlineStr">
         <is>
-          <t>Số 542/13 Bình Giã, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I137" s="7" t="inlineStr">
@@ -11140,17 +11146,17 @@
         </is>
       </c>
       <c r="K137" s="13" t="n">
-        <v>925926.0</v>
+        <v>1444800.0</v>
       </c>
       <c r="L137" s="13" t="n">
-        <v>74074.0</v>
+        <v>115584.0</v>
       </c>
       <c r="M137" s="13" t="n">
-        <v>0.0</v>
+        <v>235200.0</v>
       </c>
       <c r="N137" s="13"/>
       <c r="O137" s="13" t="n">
-        <v>1000000.0</v>
+        <v>1560384.0</v>
       </c>
       <c r="P137" s="7" t="inlineStr">
         <is>
@@ -11184,32 +11190,32 @@
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>C25TLP</t>
+          <t>C25THP</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>3502376562</t>
+          <t>3502343006</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THỰC PHẨM HƯNG LỘC PHÁT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
         <is>
-          <t>Số 542/13 Bình Giã, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I138" s="7" t="inlineStr">
@@ -11223,17 +11229,17 @@
         </is>
       </c>
       <c r="K138" s="13" t="n">
-        <v>3.2148148E7</v>
+        <v>6626740.0</v>
       </c>
       <c r="L138" s="13" t="n">
-        <v>2571852.0</v>
+        <v>530140.0</v>
       </c>
       <c r="M138" s="13" t="n">
-        <v>0.0</v>
+        <v>1254924.0</v>
       </c>
       <c r="N138" s="13"/>
       <c r="O138" s="13" t="n">
-        <v>3.472E7</v>
+        <v>7156880.0</v>
       </c>
       <c r="P138" s="7" t="inlineStr">
         <is>
@@ -11267,12 +11273,12 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>C25TLP</t>
+          <t>C25THP</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr">
@@ -11282,17 +11288,17 @@
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>3502376562</t>
+          <t>3502343006</t>
         </is>
       </c>
       <c r="G139" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THỰC PHẨM HƯNG LỘC PHÁT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>Số 542/13 Bình Giã, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I139" s="7" t="inlineStr">
@@ -11306,17 +11312,17 @@
         </is>
       </c>
       <c r="K139" s="13" t="n">
-        <v>4497549.0</v>
+        <v>592592.0</v>
       </c>
       <c r="L139" s="13" t="n">
-        <v>359804.0</v>
+        <v>47407.0</v>
       </c>
       <c r="M139" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N139" s="13"/>
       <c r="O139" s="13" t="n">
-        <v>4857353.0</v>
+        <v>639999.0</v>
       </c>
       <c r="P139" s="7" t="inlineStr">
         <is>
@@ -11350,32 +11356,32 @@
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>C25TLP</t>
+          <t>C25THP</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="E140" s="7" t="inlineStr">
         <is>
-          <t>13/12/2025</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>3502376562</t>
+          <t>3502343006</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THỰC PHẨM HƯNG LỘC PHÁT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
         </is>
       </c>
       <c r="H140" s="6" t="inlineStr">
         <is>
-          <t>Số 542/13 Bình Giã, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I140" s="7" t="inlineStr">
@@ -11389,17 +11395,17 @@
         </is>
       </c>
       <c r="K140" s="13" t="n">
-        <v>2558007.0</v>
+        <v>822222.0</v>
       </c>
       <c r="L140" s="13" t="n">
-        <v>204641.0</v>
+        <v>65778.0</v>
       </c>
       <c r="M140" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N140" s="13"/>
       <c r="O140" s="13" t="n">
-        <v>2762648.0</v>
+        <v>888000.0</v>
       </c>
       <c r="P140" s="7" t="inlineStr">
         <is>
@@ -11433,32 +11439,32 @@
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>C25TKN</t>
+          <t>C25TMP</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>04/12/2025</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>3502380738</t>
+          <t>3502356929</t>
         </is>
       </c>
       <c r="G141" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KIM NGỌC KHANG</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VẬN TẢI TÂM MINH PHÁT</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>Số 06 Nguyễn Thị Minh Khai, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 1621 Quốc lộ 55, Khu phố Long An, Xã Long Điền, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I141" s="7" t="inlineStr">
@@ -11468,21 +11474,19 @@
       </c>
       <c r="J141" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K141" s="13" t="n">
-        <v>1.4727273E7</v>
+        <v>1.53055556E8</v>
       </c>
       <c r="L141" s="13" t="n">
-        <v>1472727.0</v>
-      </c>
-      <c r="M141" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>1.2244444E7</v>
+      </c>
+      <c r="M141" s="13"/>
       <c r="N141" s="13"/>
       <c r="O141" s="13" t="n">
-        <v>1.62E7</v>
+        <v>1.653E8</v>
       </c>
       <c r="P141" s="7" t="inlineStr">
         <is>
@@ -11516,32 +11520,32 @@
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>C25TKN</t>
+          <t>C25TVT</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="E142" s="7" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>3502380738</t>
+          <t>3502358700</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KIM NGỌC KHANG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ IT VŨNG TÀU</t>
         </is>
       </c>
       <c r="H142" s="6" t="inlineStr">
         <is>
-          <t>Số 06 Nguyễn Thị Minh Khai, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>533 Nguyễn An Ninh, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I142" s="7" t="inlineStr">
@@ -11551,21 +11555,19 @@
       </c>
       <c r="J142" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K142" s="13" t="n">
-        <v>1.2954546E7</v>
+        <v>1650000.0</v>
       </c>
       <c r="L142" s="13" t="n">
-        <v>1295454.0</v>
-      </c>
-      <c r="M142" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>132000.0</v>
+      </c>
+      <c r="M142" s="13"/>
       <c r="N142" s="13"/>
       <c r="O142" s="13" t="n">
-        <v>1.425E7</v>
+        <v>1782000.0</v>
       </c>
       <c r="P142" s="7" t="inlineStr">
         <is>
@@ -11599,32 +11601,32 @@
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>C25TVV</t>
+          <t>C25TVT</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>03/12/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>3502391923</t>
+          <t>3502358700</t>
         </is>
       </c>
       <c r="G143" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH VIKGO VN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ IT VŨNG TÀU</t>
         </is>
       </c>
       <c r="H143" s="6" t="inlineStr">
         <is>
-          <t>Số 165/18/6 Đô Lương, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>533 Nguyễn An Ninh, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I143" s="7" t="inlineStr">
@@ -11638,17 +11640,15 @@
         </is>
       </c>
       <c r="K143" s="13" t="n">
-        <v>2.2592593E7</v>
+        <v>900000.0</v>
       </c>
       <c r="L143" s="13" t="n">
-        <v>1807407.0</v>
-      </c>
-      <c r="M143" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>72000.0</v>
+      </c>
+      <c r="M143" s="13"/>
       <c r="N143" s="13"/>
       <c r="O143" s="13" t="n">
-        <v>2.44E7</v>
+        <v>972000.0</v>
       </c>
       <c r="P143" s="7" t="inlineStr">
         <is>
@@ -11682,32 +11682,32 @@
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>C25TDH</t>
+          <t>C25TLP</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>03/12/2025</t>
         </is>
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>3502399055</t>
+          <t>3502376562</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr">
         <is>
-          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+          <t>CÔNG TY TNHH THỰC PHẨM HƯNG LỘC PHÁT</t>
         </is>
       </c>
       <c r="H144" s="6" t="inlineStr">
         <is>
-          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 542/13 Bình Giã, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I144" s="7" t="inlineStr">
@@ -11721,17 +11721,17 @@
         </is>
       </c>
       <c r="K144" s="13" t="n">
-        <v>1722223.0</v>
+        <v>925926.0</v>
       </c>
       <c r="L144" s="13" t="n">
-        <v>137777.0</v>
+        <v>74074.0</v>
       </c>
       <c r="M144" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N144" s="13"/>
       <c r="O144" s="13" t="n">
-        <v>1860000.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="P144" s="7" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
       </c>
       <c r="R144" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn điều chỉnh</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="S144" s="6" t="inlineStr">
@@ -11765,32 +11765,32 @@
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>C25TTT</t>
+          <t>C25TLP</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>3502425499</t>
+          <t>3502376562</t>
         </is>
       </c>
       <c r="G145" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NPP TOÀN THẮNG PH</t>
+          <t>CÔNG TY TNHH THỰC PHẨM HƯNG LỘC PHÁT</t>
         </is>
       </c>
       <c r="H145" s="6" t="inlineStr">
         <is>
-          <t>75/9/7 Phạm Hồng Thái, Phường Tam Thắng, TP.HCM</t>
+          <t>Số 542/13 Bình Giã, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I145" s="7" t="inlineStr">
@@ -11804,17 +11804,17 @@
         </is>
       </c>
       <c r="K145" s="13" t="n">
-        <v>4207407.0</v>
+        <v>3.2148148E7</v>
       </c>
       <c r="L145" s="13" t="n">
-        <v>336593.0</v>
+        <v>2571852.0</v>
       </c>
       <c r="M145" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N145" s="13"/>
       <c r="O145" s="13" t="n">
-        <v>4544000.0</v>
+        <v>3.472E7</v>
       </c>
       <c r="P145" s="7" t="inlineStr">
         <is>
@@ -11848,32 +11848,32 @@
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>C25TMH</t>
+          <t>C25TLP</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>3502426816</t>
+          <t>3502376562</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+          <t>CÔNG TY TNHH THỰC PHẨM HƯNG LỘC PHÁT</t>
         </is>
       </c>
       <c r="H146" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 542/13 Bình Giã, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I146" s="7" t="inlineStr">
@@ -11887,17 +11887,17 @@
         </is>
       </c>
       <c r="K146" s="13" t="n">
-        <v>6206399.0</v>
+        <v>4497549.0</v>
       </c>
       <c r="L146" s="13" t="n">
-        <v>496512.0</v>
+        <v>359804.0</v>
       </c>
       <c r="M146" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N146" s="13"/>
       <c r="O146" s="13" t="n">
-        <v>6702911.0</v>
+        <v>4857353.0</v>
       </c>
       <c r="P146" s="7" t="inlineStr">
         <is>
@@ -11931,32 +11931,32 @@
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>C25TMH</t>
+          <t>C25TLP</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>4486</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>13/12/2025</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>3502426816</t>
+          <t>3502376562</t>
         </is>
       </c>
       <c r="G147" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+          <t>CÔNG TY TNHH THỰC PHẨM HƯNG LỘC PHÁT</t>
         </is>
       </c>
       <c r="H147" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 542/13 Bình Giã, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I147" s="7" t="inlineStr">
@@ -11970,17 +11970,17 @@
         </is>
       </c>
       <c r="K147" s="13" t="n">
-        <v>4552733.0</v>
+        <v>2558007.0</v>
       </c>
       <c r="L147" s="13" t="n">
-        <v>364219.0</v>
+        <v>204641.0</v>
       </c>
       <c r="M147" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N147" s="13"/>
       <c r="O147" s="13" t="n">
-        <v>4916952.0</v>
+        <v>2762648.0</v>
       </c>
       <c r="P147" s="7" t="inlineStr">
         <is>
@@ -12014,32 +12014,32 @@
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>C25TMH</t>
+          <t>C25TKN</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>8864</t>
+          <t>6759</t>
         </is>
       </c>
       <c r="E148" s="7" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>3502426816</t>
+          <t>3502380738</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+          <t>CÔNG TY TNHH KIM NGỌC KHANG</t>
         </is>
       </c>
       <c r="H148" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 06 Nguyễn Thị Minh Khai, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I148" s="7" t="inlineStr">
@@ -12049,21 +12049,21 @@
       </c>
       <c r="J148" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
       <c r="K148" s="13" t="n">
-        <v>904178.0</v>
+        <v>1.4727273E7</v>
       </c>
       <c r="L148" s="13" t="n">
-        <v>72334.0</v>
+        <v>1472727.0</v>
       </c>
       <c r="M148" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N148" s="13"/>
       <c r="O148" s="13" t="n">
-        <v>976512.0</v>
+        <v>1.62E7</v>
       </c>
       <c r="P148" s="7" t="inlineStr">
         <is>
@@ -12097,32 +12097,32 @@
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>C25TMH</t>
+          <t>C25TKN</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>8875</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="E149" s="7" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>3502426816</t>
+          <t>3502380738</t>
         </is>
       </c>
       <c r="G149" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+          <t>CÔNG TY TNHH KIM NGỌC KHANG</t>
         </is>
       </c>
       <c r="H149" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 06 Nguyễn Thị Minh Khai, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I149" s="7" t="inlineStr">
@@ -12132,21 +12132,21 @@
       </c>
       <c r="J149" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
       <c r="K149" s="13" t="n">
-        <v>427778.0</v>
+        <v>1.2954546E7</v>
       </c>
       <c r="L149" s="13" t="n">
-        <v>34222.0</v>
+        <v>1295454.0</v>
       </c>
       <c r="M149" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N149" s="13"/>
       <c r="O149" s="13" t="n">
-        <v>462000.0</v>
+        <v>1.425E7</v>
       </c>
       <c r="P149" s="7" t="inlineStr">
         <is>
@@ -12180,32 +12180,32 @@
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>C25TMH</t>
+          <t>C25TVV</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>03/12/2025</t>
         </is>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>3502426816</t>
+          <t>3502391923</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+          <t>CÔNG TY TNHH VIKGO VN</t>
         </is>
       </c>
       <c r="H150" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 165/18/6 Đô Lương, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I150" s="7" t="inlineStr">
@@ -12219,17 +12219,17 @@
         </is>
       </c>
       <c r="K150" s="13" t="n">
-        <v>5978265.0</v>
+        <v>2.2592593E7</v>
       </c>
       <c r="L150" s="13" t="n">
-        <v>478261.0</v>
+        <v>1807407.0</v>
       </c>
       <c r="M150" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N150" s="13"/>
       <c r="O150" s="13" t="n">
-        <v>6456526.0</v>
+        <v>2.44E7</v>
       </c>
       <c r="P150" s="7" t="inlineStr">
         <is>
@@ -12263,32 +12263,32 @@
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>C25TMH</t>
+          <t>C25TDH</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>946</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>04/12/2025</t>
         </is>
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>3502426816</t>
+          <t>3502399055</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
         </is>
       </c>
       <c r="H151" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I151" s="7" t="inlineStr">
@@ -12302,17 +12302,17 @@
         </is>
       </c>
       <c r="K151" s="13" t="n">
-        <v>1.2272975E7</v>
+        <v>1722223.0</v>
       </c>
       <c r="L151" s="13" t="n">
-        <v>981838.0</v>
+        <v>137777.0</v>
       </c>
       <c r="M151" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N151" s="13"/>
       <c r="O151" s="13" t="n">
-        <v>1.3254813E7</v>
+        <v>1860000.0</v>
       </c>
       <c r="P151" s="7" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="R151" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn điều chỉnh</t>
         </is>
       </c>
       <c r="S151" s="6" t="inlineStr">
@@ -12346,32 +12346,32 @@
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>C25TMH</t>
+          <t>C25TTT</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>9152</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>3502426816</t>
+          <t>3502425499</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+          <t>CÔNG TY TNHH NPP TOÀN THẮNG PH</t>
         </is>
       </c>
       <c r="H152" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>75/9/7 Phạm Hồng Thái, Phường Tam Thắng, TP.HCM</t>
         </is>
       </c>
       <c r="I152" s="7" t="inlineStr">
@@ -12385,17 +12385,17 @@
         </is>
       </c>
       <c r="K152" s="13" t="n">
-        <v>3081663.0</v>
+        <v>4207407.0</v>
       </c>
       <c r="L152" s="13" t="n">
-        <v>246533.0</v>
+        <v>336593.0</v>
       </c>
       <c r="M152" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N152" s="13"/>
       <c r="O152" s="13" t="n">
-        <v>3328196.0</v>
+        <v>4544000.0</v>
       </c>
       <c r="P152" s="7" t="inlineStr">
         <is>
@@ -12434,12 +12434,12 @@
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F153" s="7" t="inlineStr">
@@ -12468,17 +12468,17 @@
         </is>
       </c>
       <c r="K153" s="13" t="n">
-        <v>1092593.0</v>
+        <v>6206399.0</v>
       </c>
       <c r="L153" s="13" t="n">
-        <v>87407.0</v>
+        <v>496512.0</v>
       </c>
       <c r="M153" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N153" s="13"/>
       <c r="O153" s="13" t="n">
-        <v>1180000.0</v>
+        <v>6702911.0</v>
       </c>
       <c r="P153" s="7" t="inlineStr">
         <is>
@@ -12517,12 +12517,12 @@
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>9233</t>
+          <t>8861</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
         <is>
-          <t>13/12/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="F154" s="7" t="inlineStr">
@@ -12551,17 +12551,17 @@
         </is>
       </c>
       <c r="K154" s="13" t="n">
-        <v>6005924.0</v>
+        <v>4552733.0</v>
       </c>
       <c r="L154" s="13" t="n">
-        <v>480474.0</v>
+        <v>364219.0</v>
       </c>
       <c r="M154" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N154" s="13"/>
       <c r="O154" s="13" t="n">
-        <v>6486398.0</v>
+        <v>4916952.0</v>
       </c>
       <c r="P154" s="7" t="inlineStr">
         <is>
@@ -12600,12 +12600,12 @@
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr">
         <is>
-          <t>13/12/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="F155" s="7" t="inlineStr">
@@ -12634,17 +12634,17 @@
         </is>
       </c>
       <c r="K155" s="13" t="n">
-        <v>117000.0</v>
+        <v>904178.0</v>
       </c>
       <c r="L155" s="13" t="n">
-        <v>9360.0</v>
+        <v>72334.0</v>
       </c>
       <c r="M155" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N155" s="13"/>
       <c r="O155" s="13" t="n">
-        <v>126360.0</v>
+        <v>976512.0</v>
       </c>
       <c r="P155" s="7" t="inlineStr">
         <is>
@@ -12678,32 +12678,32 @@
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>C25TTL</t>
+          <t>C25TMH</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>3502459466</t>
+          <t>3502426816</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THUỐC LÁ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
         </is>
       </c>
       <c r="H156" s="6" t="inlineStr">
         <is>
-          <t>39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I156" s="7" t="inlineStr">
@@ -12717,17 +12717,17 @@
         </is>
       </c>
       <c r="K156" s="13" t="n">
-        <v>2.2272727E7</v>
+        <v>427778.0</v>
       </c>
       <c r="L156" s="13" t="n">
-        <v>2227273.0</v>
+        <v>34222.0</v>
       </c>
       <c r="M156" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N156" s="13"/>
       <c r="O156" s="13" t="n">
-        <v>2.45E7</v>
+        <v>462000.0</v>
       </c>
       <c r="P156" s="7" t="inlineStr">
         <is>
@@ -12761,32 +12761,32 @@
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>C25TYY</t>
+          <t>C25TMH</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr">
         <is>
-          <t>06/12/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>3502474552</t>
+          <t>3502426816</t>
         </is>
       </c>
       <c r="G157" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
         </is>
       </c>
       <c r="H157" s="6" t="inlineStr">
         <is>
-          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I157" s="7" t="inlineStr">
@@ -12800,15 +12800,17 @@
         </is>
       </c>
       <c r="K157" s="13" t="n">
-        <v>2731440.0</v>
+        <v>5978265.0</v>
       </c>
       <c r="L157" s="13" t="n">
-        <v>218515.0</v>
-      </c>
-      <c r="M157" s="13"/>
+        <v>478261.0</v>
+      </c>
+      <c r="M157" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N157" s="13"/>
       <c r="O157" s="13" t="n">
-        <v>2949955.0</v>
+        <v>6456526.0</v>
       </c>
       <c r="P157" s="7" t="inlineStr">
         <is>
@@ -12842,32 +12844,32 @@
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>C25TYY</t>
+          <t>C25TMH</t>
         </is>
       </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>3502474552</t>
+          <t>3502426816</t>
         </is>
       </c>
       <c r="G158" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
         </is>
       </c>
       <c r="H158" s="6" t="inlineStr">
         <is>
-          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I158" s="7" t="inlineStr">
@@ -12881,15 +12883,17 @@
         </is>
       </c>
       <c r="K158" s="13" t="n">
-        <v>2731440.0</v>
+        <v>1.2272975E7</v>
       </c>
       <c r="L158" s="13" t="n">
-        <v>218515.0</v>
-      </c>
-      <c r="M158" s="13"/>
+        <v>981838.0</v>
+      </c>
+      <c r="M158" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N158" s="13"/>
       <c r="O158" s="13" t="n">
-        <v>2949955.0</v>
+        <v>1.3254813E7</v>
       </c>
       <c r="P158" s="7" t="inlineStr">
         <is>
@@ -12923,32 +12927,32 @@
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>C25TYY</t>
+          <t>C25TMH</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="F159" s="7" t="inlineStr">
         <is>
-          <t>3502478885</t>
+          <t>3502426816</t>
         </is>
       </c>
       <c r="G159" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ LINH CHÂU VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
         </is>
       </c>
       <c r="H159" s="6" t="inlineStr">
         <is>
-          <t>Số 43 Đường Nguyễn Quyền, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I159" s="7" t="inlineStr">
@@ -12962,17 +12966,17 @@
         </is>
       </c>
       <c r="K159" s="13" t="n">
-        <v>1.2037037E8</v>
+        <v>3081663.0</v>
       </c>
       <c r="L159" s="13" t="n">
-        <v>9629630.0</v>
+        <v>246533.0</v>
       </c>
       <c r="M159" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N159" s="13"/>
       <c r="O159" s="13" t="n">
-        <v>1.3E8</v>
+        <v>3328196.0</v>
       </c>
       <c r="P159" s="7" t="inlineStr">
         <is>
@@ -13006,12 +13010,12 @@
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>C25THN</t>
+          <t>C25TMH</t>
         </is>
       </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr">
@@ -13021,17 +13025,17 @@
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>3502509861</t>
+          <t>3502426816</t>
         </is>
       </c>
       <c r="G160" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ KINH DOANH TM DV HOÀNG NAM</t>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
         </is>
       </c>
       <c r="H160" s="6" t="inlineStr">
         <is>
-          <t>780 đường 2 tháng 9, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I160" s="7" t="inlineStr">
@@ -13045,17 +13049,17 @@
         </is>
       </c>
       <c r="K160" s="13" t="n">
-        <v>4262499.0</v>
+        <v>1092593.0</v>
       </c>
       <c r="L160" s="13" t="n">
-        <v>341000.0</v>
+        <v>87407.0</v>
       </c>
       <c r="M160" s="13" t="n">
-        <v>43056.0</v>
+        <v>0.0</v>
       </c>
       <c r="N160" s="13"/>
       <c r="O160" s="13" t="n">
-        <v>4603499.0</v>
+        <v>1180000.0</v>
       </c>
       <c r="P160" s="7" t="inlineStr">
         <is>
@@ -13089,32 +13093,32 @@
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>C25TYY</t>
+          <t>C25TMH</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>9233</t>
         </is>
       </c>
       <c r="E161" s="7" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>13/12/2025</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
-          <t>3502536551</t>
+          <t>3502426816</t>
         </is>
       </c>
       <c r="G161" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHƯƠNG AN KỲ</t>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
         </is>
       </c>
       <c r="H161" s="6" t="inlineStr">
         <is>
-          <t>219 Võ Thị Sáu, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I161" s="7" t="inlineStr">
@@ -13128,17 +13132,17 @@
         </is>
       </c>
       <c r="K161" s="13" t="n">
-        <v>888889.0</v>
+        <v>6005924.0</v>
       </c>
       <c r="L161" s="13" t="n">
-        <v>71111.0</v>
+        <v>480474.0</v>
       </c>
       <c r="M161" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N161" s="13"/>
       <c r="O161" s="13" t="n">
-        <v>960000.0</v>
+        <v>6486398.0</v>
       </c>
       <c r="P161" s="7" t="inlineStr">
         <is>
@@ -13172,32 +13176,32 @@
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>C25TYY</t>
+          <t>C25TMH</t>
         </is>
       </c>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>9247</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>13/12/2025</t>
         </is>
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
-          <t>3502536551</t>
+          <t>3502426816</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHƯƠNG AN KỲ</t>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
         </is>
       </c>
       <c r="H162" s="6" t="inlineStr">
         <is>
-          <t>219 Võ Thị Sáu, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I162" s="7" t="inlineStr">
@@ -13211,17 +13215,17 @@
         </is>
       </c>
       <c r="K162" s="13" t="n">
-        <v>4288889.0</v>
+        <v>117000.0</v>
       </c>
       <c r="L162" s="13" t="n">
-        <v>343111.0</v>
+        <v>9360.0</v>
       </c>
       <c r="M162" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N162" s="13"/>
       <c r="O162" s="13" t="n">
-        <v>4632000.0</v>
+        <v>126360.0</v>
       </c>
       <c r="P162" s="7" t="inlineStr">
         <is>
@@ -13255,32 +13259,32 @@
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>C25TPM</t>
+          <t>C25TTL</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>10473</t>
         </is>
       </c>
       <c r="E163" s="7" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="F163" s="7" t="inlineStr">
         <is>
-          <t>3502547345</t>
+          <t>3502459466</t>
         </is>
       </c>
       <c r="G163" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ KHANG PHÚC MINH</t>
+          <t>CÔNG TY TNHH THUỐC LÁ VŨNG TÀU</t>
         </is>
       </c>
       <c r="H163" s="6" t="inlineStr">
         <is>
-          <t>Số 1621 Quốc lộ 55, Khu phố Long An, Xã Long Điền, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I163" s="7" t="inlineStr">
@@ -13294,17 +13298,17 @@
         </is>
       </c>
       <c r="K163" s="13" t="n">
-        <v>1.03909091E8</v>
+        <v>2.2272727E7</v>
       </c>
       <c r="L163" s="13" t="n">
-        <v>1.0390909E7</v>
+        <v>2227273.0</v>
       </c>
       <c r="M163" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N163" s="13"/>
       <c r="O163" s="13" t="n">
-        <v>1.143E8</v>
+        <v>2.45E7</v>
       </c>
       <c r="P163" s="7" t="inlineStr">
         <is>
@@ -13338,12 +13342,12 @@
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>C25THB</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D164" s="7" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="E164" s="7" t="inlineStr">
@@ -13353,17 +13357,17 @@
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
-          <t>3502547803</t>
+          <t>3502474552</t>
         </is>
       </c>
       <c r="G164" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HẢI HÀ BÌNH</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
         </is>
       </c>
       <c r="H164" s="6" t="inlineStr">
         <is>
-          <t>292/16B đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I164" s="7" t="inlineStr">
@@ -13377,17 +13381,15 @@
         </is>
       </c>
       <c r="K164" s="13" t="n">
-        <v>1700000.0</v>
+        <v>2731440.0</v>
       </c>
       <c r="L164" s="13" t="n">
-        <v>136000.0</v>
-      </c>
-      <c r="M164" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>218515.0</v>
+      </c>
+      <c r="M164" s="13"/>
       <c r="N164" s="13"/>
       <c r="O164" s="13" t="n">
-        <v>1836000.0</v>
+        <v>2949955.0</v>
       </c>
       <c r="P164" s="7" t="inlineStr">
         <is>
@@ -13421,32 +13423,32 @@
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>C25TMQ</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>3502548074</t>
+          <t>3502474552</t>
         </is>
       </c>
       <c r="G165" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
         </is>
       </c>
       <c r="H165" s="6" t="inlineStr">
         <is>
-          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I165" s="7" t="inlineStr">
@@ -13460,15 +13462,15 @@
         </is>
       </c>
       <c r="K165" s="13" t="n">
-        <v>3005370.0</v>
+        <v>2731440.0</v>
       </c>
       <c r="L165" s="13" t="n">
-        <v>240430.0</v>
+        <v>218515.0</v>
       </c>
       <c r="M165" s="13"/>
       <c r="N165" s="13"/>
       <c r="O165" s="13" t="n">
-        <v>3245800.0</v>
+        <v>2949955.0</v>
       </c>
       <c r="P165" s="7" t="inlineStr">
         <is>
@@ -13502,32 +13504,32 @@
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>C25TMQ</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="E166" s="7" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>3502548074</t>
+          <t>3502478885</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ LINH CHÂU VŨNG TÀU</t>
         </is>
       </c>
       <c r="H166" s="6" t="inlineStr">
         <is>
-          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 43 Đường Nguyễn Quyền, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I166" s="7" t="inlineStr">
@@ -13541,15 +13543,17 @@
         </is>
       </c>
       <c r="K166" s="13" t="n">
-        <v>3525410.0</v>
+        <v>1.2037037E8</v>
       </c>
       <c r="L166" s="13" t="n">
-        <v>282033.0</v>
-      </c>
-      <c r="M166" s="13"/>
+        <v>9629630.0</v>
+      </c>
+      <c r="M166" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N166" s="13"/>
       <c r="O166" s="13" t="n">
-        <v>3807443.0</v>
+        <v>1.3E8</v>
       </c>
       <c r="P166" s="7" t="inlineStr">
         <is>
@@ -13583,32 +13587,32 @@
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>C25TMQ</t>
+          <t>C25THN</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>708</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr">
         <is>
-          <t>3502548074</t>
+          <t>3502509861</t>
         </is>
       </c>
       <c r="G167" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ KINH DOANH TM DV HOÀNG NAM</t>
         </is>
       </c>
       <c r="H167" s="6" t="inlineStr">
         <is>
-          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>780 đường 2 tháng 9, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I167" s="7" t="inlineStr">
@@ -13622,15 +13626,17 @@
         </is>
       </c>
       <c r="K167" s="13" t="n">
-        <v>2805120.0</v>
+        <v>4262499.0</v>
       </c>
       <c r="L167" s="13" t="n">
-        <v>224410.0</v>
-      </c>
-      <c r="M167" s="13"/>
+        <v>341000.0</v>
+      </c>
+      <c r="M167" s="13" t="n">
+        <v>43056.0</v>
+      </c>
       <c r="N167" s="13"/>
       <c r="O167" s="13" t="n">
-        <v>3029530.0</v>
+        <v>4603499.0</v>
       </c>
       <c r="P167" s="7" t="inlineStr">
         <is>
@@ -13664,32 +13670,32 @@
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>C25TMQ</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="E168" s="7" t="inlineStr">
         <is>
-          <t>13/12/2025</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>3502548074</t>
+          <t>3502536551</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHƯƠNG AN KỲ</t>
         </is>
       </c>
       <c r="H168" s="6" t="inlineStr">
         <is>
-          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>219 Võ Thị Sáu, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I168" s="7" t="inlineStr">
@@ -13703,15 +13709,17 @@
         </is>
       </c>
       <c r="K168" s="13" t="n">
-        <v>5894030.0</v>
+        <v>888889.0</v>
       </c>
       <c r="L168" s="13" t="n">
-        <v>471522.0</v>
-      </c>
-      <c r="M168" s="13"/>
+        <v>71111.0</v>
+      </c>
+      <c r="M168" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N168" s="13"/>
       <c r="O168" s="13" t="n">
-        <v>6365552.0</v>
+        <v>960000.0</v>
       </c>
       <c r="P168" s="7" t="inlineStr">
         <is>
@@ -13745,32 +13753,32 @@
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>C25TDD</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="E169" s="7" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>3502548116</t>
+          <t>3502536551</t>
         </is>
       </c>
       <c r="G169" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHƯƠNG AN KỲ</t>
         </is>
       </c>
       <c r="H169" s="6" t="inlineStr">
         <is>
-          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>219 Võ Thị Sáu, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I169" s="7" t="inlineStr">
@@ -13784,17 +13792,17 @@
         </is>
       </c>
       <c r="K169" s="13" t="n">
-        <v>1.1587963E7</v>
+        <v>4288889.0</v>
       </c>
       <c r="L169" s="13" t="n">
-        <v>927037.0</v>
+        <v>343111.0</v>
       </c>
       <c r="M169" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N169" s="13"/>
       <c r="O169" s="13" t="n">
-        <v>1.2515E7</v>
+        <v>4632000.0</v>
       </c>
       <c r="P169" s="7" t="inlineStr">
         <is>
@@ -13808,7 +13816,7 @@
       </c>
       <c r="R169" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn đã bị thay thế</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="S169" s="6" t="inlineStr">
@@ -13828,32 +13836,32 @@
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>C25TDD</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>3502548116</t>
+          <t>3502536551</t>
         </is>
       </c>
       <c r="G170" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHƯƠNG AN KỲ</t>
         </is>
       </c>
       <c r="H170" s="6" t="inlineStr">
         <is>
-          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>219 Võ Thị Sáu, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I170" s="7" t="inlineStr">
@@ -13867,17 +13875,17 @@
         </is>
       </c>
       <c r="K170" s="13" t="n">
-        <v>1.1310185E7</v>
+        <v>8440422.0</v>
       </c>
       <c r="L170" s="13" t="n">
-        <v>904815.0</v>
+        <v>675234.0</v>
       </c>
       <c r="M170" s="13" t="n">
-        <v>0.0</v>
+        <v>38467.0</v>
       </c>
       <c r="N170" s="13"/>
       <c r="O170" s="13" t="n">
-        <v>1.2215E7</v>
+        <v>9115656.0</v>
       </c>
       <c r="P170" s="7" t="inlineStr">
         <is>
@@ -13891,7 +13899,7 @@
       </c>
       <c r="R170" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn thay thế</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="S170" s="6" t="inlineStr">
@@ -13911,32 +13919,32 @@
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>C25TDD</t>
+          <t>C25TPM</t>
         </is>
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>260</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>04/12/2025</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>3502548116</t>
+          <t>3502547345</t>
         </is>
       </c>
       <c r="G171" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ KHANG PHÚC MINH</t>
         </is>
       </c>
       <c r="H171" s="6" t="inlineStr">
         <is>
-          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 1621 Quốc lộ 55, Khu phố Long An, Xã Long Điền, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I171" s="7" t="inlineStr">
@@ -13950,17 +13958,17 @@
         </is>
       </c>
       <c r="K171" s="13" t="n">
-        <v>1.695463E7</v>
+        <v>1.03909091E8</v>
       </c>
       <c r="L171" s="13" t="n">
-        <v>1356370.0</v>
+        <v>1.0390909E7</v>
       </c>
       <c r="M171" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N171" s="13"/>
       <c r="O171" s="13" t="n">
-        <v>1.8311E7</v>
+        <v>1.143E8</v>
       </c>
       <c r="P171" s="7" t="inlineStr">
         <is>
@@ -13994,32 +14002,32 @@
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>C25TDD</t>
+          <t>C25THB</t>
         </is>
       </c>
       <c r="D172" s="7" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E172" s="7" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>06/12/2025</t>
         </is>
       </c>
       <c r="F172" s="7" t="inlineStr">
         <is>
-          <t>3502548116</t>
+          <t>3502547803</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HẢI HÀ BÌNH</t>
         </is>
       </c>
       <c r="H172" s="6" t="inlineStr">
         <is>
-          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>292/16B đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I172" s="7" t="inlineStr">
@@ -14033,17 +14041,17 @@
         </is>
       </c>
       <c r="K172" s="13" t="n">
-        <v>5814815.0</v>
+        <v>1700000.0</v>
       </c>
       <c r="L172" s="13" t="n">
-        <v>465185.0</v>
+        <v>136000.0</v>
       </c>
       <c r="M172" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N172" s="13"/>
       <c r="O172" s="13" t="n">
-        <v>6280000.0</v>
+        <v>1836000.0</v>
       </c>
       <c r="P172" s="7" t="inlineStr">
         <is>
@@ -14077,32 +14085,32 @@
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>C25TDD</t>
+          <t>C25TMQ</t>
         </is>
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>265</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
-          <t>3502548116</t>
+          <t>3502548074</t>
         </is>
       </c>
       <c r="G173" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
         </is>
       </c>
       <c r="H173" s="6" t="inlineStr">
         <is>
-          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I173" s="7" t="inlineStr">
@@ -14116,17 +14124,15 @@
         </is>
       </c>
       <c r="K173" s="13" t="n">
-        <v>3136111.0</v>
+        <v>3005370.0</v>
       </c>
       <c r="L173" s="13" t="n">
-        <v>250889.0</v>
-      </c>
-      <c r="M173" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>240430.0</v>
+      </c>
+      <c r="M173" s="13"/>
       <c r="N173" s="13"/>
       <c r="O173" s="13" t="n">
-        <v>3387000.0</v>
+        <v>3245800.0</v>
       </c>
       <c r="P173" s="7" t="inlineStr">
         <is>
@@ -14160,32 +14166,32 @@
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>C25TMD</t>
+          <t>C25TMQ</t>
         </is>
       </c>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>282</t>
         </is>
       </c>
       <c r="E174" s="7" t="inlineStr">
         <is>
-          <t>03/12/2025</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="F174" s="7" t="inlineStr">
         <is>
-          <t>3502548846</t>
+          <t>3502548074</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ MD VŨNG TÀU</t>
+          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
         </is>
       </c>
       <c r="H174" s="6" t="inlineStr">
         <is>
-          <t>25/42/33 Nguyễn Hữu Cảnh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I174" s="7" t="inlineStr">
@@ -14199,17 +14205,15 @@
         </is>
       </c>
       <c r="K174" s="13" t="n">
-        <v>8379648.0</v>
+        <v>3525410.0</v>
       </c>
       <c r="L174" s="13" t="n">
-        <v>670372.0</v>
-      </c>
-      <c r="M174" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>282033.0</v>
+      </c>
+      <c r="M174" s="13"/>
       <c r="N174" s="13"/>
       <c r="O174" s="13" t="n">
-        <v>9050020.0</v>
+        <v>3807443.0</v>
       </c>
       <c r="P174" s="7" t="inlineStr">
         <is>
@@ -14243,12 +14247,12 @@
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>C25TTD</t>
+          <t>C25TMQ</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E175" s="7" t="inlineStr">
@@ -14258,17 +14262,17 @@
       </c>
       <c r="F175" s="7" t="inlineStr">
         <is>
-          <t>3502549800</t>
+          <t>3502548074</t>
         </is>
       </c>
       <c r="G175" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH B.A PHÁT TRƯỜNG THỊNH</t>
+          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
         </is>
       </c>
       <c r="H175" s="6" t="inlineStr">
         <is>
-          <t>121A/1 Huyền Trân Công Chúa, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
+          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I175" s="7" t="inlineStr">
@@ -14278,21 +14282,19 @@
       </c>
       <c r="J175" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K175" s="13" t="n">
-        <v>1623040.0</v>
+        <v>2805120.0</v>
       </c>
       <c r="L175" s="13" t="n">
-        <v>120986.0</v>
-      </c>
-      <c r="M175" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>224410.0</v>
+      </c>
+      <c r="M175" s="13"/>
       <c r="N175" s="13"/>
       <c r="O175" s="13" t="n">
-        <v>1744026.0</v>
+        <v>3029530.0</v>
       </c>
       <c r="P175" s="7" t="inlineStr">
         <is>
@@ -14326,32 +14328,32 @@
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TMQ</t>
         </is>
       </c>
       <c r="D176" s="7" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>293</t>
         </is>
       </c>
       <c r="E176" s="7" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>13/12/2025</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502548074</t>
         </is>
       </c>
       <c r="G176" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
         </is>
       </c>
       <c r="H176" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I176" s="7" t="inlineStr">
@@ -14365,17 +14367,15 @@
         </is>
       </c>
       <c r="K176" s="13" t="n">
-        <v>1.0730424E7</v>
+        <v>5894030.0</v>
       </c>
       <c r="L176" s="13" t="n">
-        <v>858434.0</v>
-      </c>
-      <c r="M176" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>471522.0</v>
+      </c>
+      <c r="M176" s="13"/>
       <c r="N176" s="13"/>
       <c r="O176" s="13" t="n">
-        <v>1.1588858E7</v>
+        <v>6365552.0</v>
       </c>
       <c r="P176" s="7" t="inlineStr">
         <is>
@@ -14409,32 +14409,32 @@
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TMQ</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>299</t>
         </is>
       </c>
       <c r="E177" s="7" t="inlineStr">
         <is>
-          <t>06/12/2025</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502548074</t>
         </is>
       </c>
       <c r="G177" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
         </is>
       </c>
       <c r="H177" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I177" s="7" t="inlineStr">
@@ -14448,17 +14448,15 @@
         </is>
       </c>
       <c r="K177" s="13" t="n">
-        <v>2225480.0</v>
+        <v>2650000.0</v>
       </c>
       <c r="L177" s="13" t="n">
-        <v>178038.0</v>
-      </c>
-      <c r="M177" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>212000.0</v>
+      </c>
+      <c r="M177" s="13"/>
       <c r="N177" s="13"/>
       <c r="O177" s="13" t="n">
-        <v>2403518.0</v>
+        <v>2862000.0</v>
       </c>
       <c r="P177" s="7" t="inlineStr">
         <is>
@@ -14492,32 +14490,32 @@
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TDD</t>
         </is>
       </c>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>869</t>
         </is>
       </c>
       <c r="E178" s="7" t="inlineStr">
         <is>
-          <t>06/12/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502548116</t>
         </is>
       </c>
       <c r="G178" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH ĐỨC DẬT</t>
         </is>
       </c>
       <c r="H178" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I178" s="7" t="inlineStr">
@@ -14531,17 +14529,17 @@
         </is>
       </c>
       <c r="K178" s="13" t="n">
-        <v>589422.0</v>
+        <v>1.1587963E7</v>
       </c>
       <c r="L178" s="13" t="n">
-        <v>47154.0</v>
+        <v>927037.0</v>
       </c>
       <c r="M178" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N178" s="13"/>
       <c r="O178" s="13" t="n">
-        <v>636576.0</v>
+        <v>1.2515E7</v>
       </c>
       <c r="P178" s="7" t="inlineStr">
         <is>
@@ -14555,7 +14553,7 @@
       </c>
       <c r="R178" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị thay thế</t>
         </is>
       </c>
       <c r="S178" s="6" t="inlineStr">
@@ -14575,32 +14573,32 @@
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TDD</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>6447</t>
+          <t>928</t>
         </is>
       </c>
       <c r="E179" s="7" t="inlineStr">
         <is>
-          <t>06/12/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502548116</t>
         </is>
       </c>
       <c r="G179" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH ĐỨC DẬT</t>
         </is>
       </c>
       <c r="H179" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I179" s="7" t="inlineStr">
@@ -14614,17 +14612,17 @@
         </is>
       </c>
       <c r="K179" s="13" t="n">
-        <v>1.6889824E7</v>
+        <v>1.1310185E7</v>
       </c>
       <c r="L179" s="13" t="n">
-        <v>1351186.0</v>
+        <v>904815.0</v>
       </c>
       <c r="M179" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N179" s="13"/>
       <c r="O179" s="13" t="n">
-        <v>1.824101E7</v>
+        <v>1.2215E7</v>
       </c>
       <c r="P179" s="7" t="inlineStr">
         <is>
@@ -14638,7 +14636,7 @@
       </c>
       <c r="R179" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn thay thế</t>
         </is>
       </c>
       <c r="S179" s="6" t="inlineStr">
@@ -14658,32 +14656,32 @@
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TDD</t>
         </is>
       </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>952</t>
         </is>
       </c>
       <c r="E180" s="7" t="inlineStr">
         <is>
-          <t>07/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502548116</t>
         </is>
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH ĐỨC DẬT</t>
         </is>
       </c>
       <c r="H180" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I180" s="7" t="inlineStr">
@@ -14697,17 +14695,17 @@
         </is>
       </c>
       <c r="K180" s="13" t="n">
-        <v>6214223.0</v>
+        <v>1.695463E7</v>
       </c>
       <c r="L180" s="13" t="n">
-        <v>497138.0</v>
+        <v>1356370.0</v>
       </c>
       <c r="M180" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N180" s="13"/>
       <c r="O180" s="13" t="n">
-        <v>6711361.0</v>
+        <v>1.8311E7</v>
       </c>
       <c r="P180" s="7" t="inlineStr">
         <is>
@@ -14741,12 +14739,12 @@
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TDD</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>6797</t>
+          <t>982</t>
         </is>
       </c>
       <c r="E181" s="7" t="inlineStr">
@@ -14756,17 +14754,17 @@
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502548116</t>
         </is>
       </c>
       <c r="G181" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH ĐỨC DẬT</t>
         </is>
       </c>
       <c r="H181" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I181" s="7" t="inlineStr">
@@ -14780,17 +14778,17 @@
         </is>
       </c>
       <c r="K181" s="13" t="n">
-        <v>1276706.0</v>
+        <v>5814815.0</v>
       </c>
       <c r="L181" s="13" t="n">
-        <v>102136.0</v>
+        <v>465185.0</v>
       </c>
       <c r="M181" s="13" t="n">
-        <v>103782.0</v>
+        <v>0.0</v>
       </c>
       <c r="N181" s="13"/>
       <c r="O181" s="13" t="n">
-        <v>1378842.0</v>
+        <v>6280000.0</v>
       </c>
       <c r="P181" s="7" t="inlineStr">
         <is>
@@ -14804,7 +14802,7 @@
       </c>
       <c r="R181" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn thay thế</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="S181" s="6" t="inlineStr">
@@ -14824,32 +14822,32 @@
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TDD</t>
         </is>
       </c>
       <c r="D182" s="7" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>999</t>
         </is>
       </c>
       <c r="E182" s="7" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502548116</t>
         </is>
       </c>
       <c r="G182" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH ĐỨC DẬT</t>
         </is>
       </c>
       <c r="H182" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I182" s="7" t="inlineStr">
@@ -14863,17 +14861,17 @@
         </is>
       </c>
       <c r="K182" s="13" t="n">
-        <v>1.288018E7</v>
+        <v>3136111.0</v>
       </c>
       <c r="L182" s="13" t="n">
-        <v>1030414.0</v>
+        <v>250889.0</v>
       </c>
       <c r="M182" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N182" s="13"/>
       <c r="O182" s="13" t="n">
-        <v>1.3910594E7</v>
+        <v>3387000.0</v>
       </c>
       <c r="P182" s="7" t="inlineStr">
         <is>
@@ -14907,32 +14905,32 @@
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TMD</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>91</t>
         </is>
       </c>
       <c r="E183" s="7" t="inlineStr">
         <is>
-          <t>13/12/2025</t>
+          <t>03/12/2025</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502548846</t>
         </is>
       </c>
       <c r="G183" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ MD VŨNG TÀU</t>
         </is>
       </c>
       <c r="H183" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>25/42/33 Nguyễn Hữu Cảnh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I183" s="7" t="inlineStr">
@@ -14946,17 +14944,17 @@
         </is>
       </c>
       <c r="K183" s="13" t="n">
-        <v>4837290.0</v>
+        <v>8379648.0</v>
       </c>
       <c r="L183" s="13" t="n">
-        <v>386983.0</v>
+        <v>670372.0</v>
       </c>
       <c r="M183" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N183" s="13"/>
       <c r="O183" s="13" t="n">
-        <v>5224273.0</v>
+        <v>9050020.0</v>
       </c>
       <c r="P183" s="7" t="inlineStr">
         <is>
@@ -14990,32 +14988,32 @@
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TTD</t>
         </is>
       </c>
       <c r="D184" s="7" t="inlineStr">
         <is>
-          <t>7375</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E184" s="7" t="inlineStr">
         <is>
-          <t>15/12/2025</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502549800</t>
         </is>
       </c>
       <c r="G184" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH B.A PHÁT TRƯỜNG THỊNH</t>
         </is>
       </c>
       <c r="H184" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>121A/1 Huyền Trân Công Chúa, Phường Tam Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I184" s="7" t="inlineStr">
@@ -15025,21 +15023,21 @@
       </c>
       <c r="J184" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
       <c r="K184" s="13" t="n">
-        <v>4573319.0</v>
+        <v>1623040.0</v>
       </c>
       <c r="L184" s="13" t="n">
-        <v>365866.0</v>
+        <v>120986.0</v>
       </c>
       <c r="M184" s="13" t="n">
-        <v>184425.0</v>
+        <v>0.0</v>
       </c>
       <c r="N184" s="13"/>
       <c r="O184" s="13" t="n">
-        <v>4939185.0</v>
+        <v>1744026.0</v>
       </c>
       <c r="P184" s="7" t="inlineStr">
         <is>
@@ -15073,32 +15071,32 @@
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>C25THB</t>
+          <t>C25THP</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="E185" s="7" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>3502552641</t>
+          <t>3502550066</t>
         </is>
       </c>
       <c r="G185" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HB COFFEE</t>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
         </is>
       </c>
       <c r="H185" s="6" t="inlineStr">
         <is>
-          <t>24 Huỳnh Văn Hớn, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I185" s="7" t="inlineStr">
@@ -15112,17 +15110,17 @@
         </is>
       </c>
       <c r="K185" s="13" t="n">
-        <v>2657400.0</v>
+        <v>1.0730424E7</v>
       </c>
       <c r="L185" s="13" t="n">
-        <v>212592.0</v>
+        <v>858434.0</v>
       </c>
       <c r="M185" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N185" s="13"/>
       <c r="O185" s="13" t="n">
-        <v>2869992.0</v>
+        <v>1.1588858E7</v>
       </c>
       <c r="P185" s="7" t="inlineStr">
         <is>
@@ -15156,32 +15154,32 @@
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>C25THB</t>
+          <t>C25THP</t>
         </is>
       </c>
       <c r="D186" s="7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>6445</t>
         </is>
       </c>
       <c r="E186" s="7" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>06/12/2025</t>
         </is>
       </c>
       <c r="F186" s="7" t="inlineStr">
         <is>
-          <t>3502552641</t>
+          <t>3502550066</t>
         </is>
       </c>
       <c r="G186" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HB COFFEE</t>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
         </is>
       </c>
       <c r="H186" s="6" t="inlineStr">
         <is>
-          <t>24 Huỳnh Văn Hớn, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I186" s="7" t="inlineStr">
@@ -15195,17 +15193,17 @@
         </is>
       </c>
       <c r="K186" s="13" t="n">
-        <v>4168970.0</v>
+        <v>2225480.0</v>
       </c>
       <c r="L186" s="13" t="n">
-        <v>333518.0</v>
+        <v>178038.0</v>
       </c>
       <c r="M186" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N186" s="13"/>
       <c r="O186" s="13" t="n">
-        <v>4502488.0</v>
+        <v>2403518.0</v>
       </c>
       <c r="P186" s="7" t="inlineStr">
         <is>
@@ -15239,32 +15237,32 @@
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>C25TVT</t>
+          <t>C25THP</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="E187" s="7" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>06/12/2025</t>
         </is>
       </c>
       <c r="F187" s="7" t="inlineStr">
         <is>
-          <t>3700696229-003</t>
+          <t>3502550066</t>
         </is>
       </c>
       <c r="G187" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN THƯƠNG MẠI BIA SÀI GÒN MIỀN ĐÔNG TẠI BÀ RỊA - VŨNG TÀU</t>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
         </is>
       </c>
       <c r="H187" s="6" t="inlineStr">
         <is>
-          <t>Số 6 Phan Đình Phùng, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I187" s="7" t="inlineStr">
@@ -15274,36 +15272,866 @@
       </c>
       <c r="J187" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THANH HƯƠNG BẾN ĐÌNH  - ĐIỂM BÁN C2 THÙY HƯƠNG</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K187" s="13" t="n">
+        <v>589422.0</v>
+      </c>
+      <c r="L187" s="13" t="n">
+        <v>47154.0</v>
+      </c>
+      <c r="M187" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="L187" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M187" s="13"/>
       <c r="N187" s="13"/>
       <c r="O187" s="13" t="n">
+        <v>636576.0</v>
+      </c>
+      <c r="P187" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q187" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R187" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S187" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>182.0</v>
+      </c>
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D188" s="7" t="inlineStr">
+        <is>
+          <t>6447</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>06/12/2025</t>
+        </is>
+      </c>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G188" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H188" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I188" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J188" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K188" s="13" t="n">
+        <v>1.6889824E7</v>
+      </c>
+      <c r="L188" s="13" t="n">
+        <v>1351186.0</v>
+      </c>
+      <c r="M188" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="P187" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q187" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R187" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S187" s="6" t="inlineStr">
+      <c r="N188" s="13"/>
+      <c r="O188" s="13" t="n">
+        <v>1.824101E7</v>
+      </c>
+      <c r="P188" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q188" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R188" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S188" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>183.0</v>
+      </c>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D189" s="7" t="inlineStr">
+        <is>
+          <t>6464</t>
+        </is>
+      </c>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>07/12/2025</t>
+        </is>
+      </c>
+      <c r="F189" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G189" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H189" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I189" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J189" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K189" s="13" t="n">
+        <v>6214223.0</v>
+      </c>
+      <c r="L189" s="13" t="n">
+        <v>497138.0</v>
+      </c>
+      <c r="M189" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N189" s="13"/>
+      <c r="O189" s="13" t="n">
+        <v>6711361.0</v>
+      </c>
+      <c r="P189" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q189" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R189" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S189" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>184.0</v>
+      </c>
+      <c r="B190" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>6797</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G190" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H190" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I190" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J190" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K190" s="13" t="n">
+        <v>1276706.0</v>
+      </c>
+      <c r="L190" s="13" t="n">
+        <v>102136.0</v>
+      </c>
+      <c r="M190" s="13" t="n">
+        <v>103782.0</v>
+      </c>
+      <c r="N190" s="13"/>
+      <c r="O190" s="13" t="n">
+        <v>1378842.0</v>
+      </c>
+      <c r="P190" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q190" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R190" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn thay thế</t>
+        </is>
+      </c>
+      <c r="S190" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>185.0</v>
+      </c>
+      <c r="B191" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C191" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D191" s="7" t="inlineStr">
+        <is>
+          <t>6803</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G191" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H191" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I191" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J191" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K191" s="13" t="n">
+        <v>1.288018E7</v>
+      </c>
+      <c r="L191" s="13" t="n">
+        <v>1030414.0</v>
+      </c>
+      <c r="M191" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N191" s="13"/>
+      <c r="O191" s="13" t="n">
+        <v>1.3910594E7</v>
+      </c>
+      <c r="P191" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q191" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R191" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S191" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="n">
+        <v>186.0</v>
+      </c>
+      <c r="B192" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C192" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D192" s="7" t="inlineStr">
+        <is>
+          <t>7173</t>
+        </is>
+      </c>
+      <c r="E192" s="7" t="inlineStr">
+        <is>
+          <t>13/12/2025</t>
+        </is>
+      </c>
+      <c r="F192" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G192" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H192" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I192" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J192" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K192" s="13" t="n">
+        <v>4837290.0</v>
+      </c>
+      <c r="L192" s="13" t="n">
+        <v>386983.0</v>
+      </c>
+      <c r="M192" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N192" s="13"/>
+      <c r="O192" s="13" t="n">
+        <v>5224273.0</v>
+      </c>
+      <c r="P192" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q192" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R192" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S192" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="n">
+        <v>187.0</v>
+      </c>
+      <c r="B193" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C193" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D193" s="7" t="inlineStr">
+        <is>
+          <t>7375</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F193" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G193" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H193" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I193" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J193" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K193" s="13" t="n">
+        <v>4573319.0</v>
+      </c>
+      <c r="L193" s="13" t="n">
+        <v>365866.0</v>
+      </c>
+      <c r="M193" s="13" t="n">
+        <v>184425.0</v>
+      </c>
+      <c r="N193" s="13"/>
+      <c r="O193" s="13" t="n">
+        <v>4939185.0</v>
+      </c>
+      <c r="P193" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q193" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R193" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S193" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="n">
+        <v>188.0</v>
+      </c>
+      <c r="B194" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D194" s="7" t="inlineStr">
+        <is>
+          <t>7410</t>
+        </is>
+      </c>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
+          <t>16/12/2025</t>
+        </is>
+      </c>
+      <c r="F194" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G194" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H194" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I194" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J194" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K194" s="13" t="n">
+        <v>957529.0</v>
+      </c>
+      <c r="L194" s="13" t="n">
+        <v>76602.0</v>
+      </c>
+      <c r="M194" s="13" t="n">
+        <v>77837.0</v>
+      </c>
+      <c r="N194" s="13"/>
+      <c r="O194" s="13" t="n">
+        <v>1034131.0</v>
+      </c>
+      <c r="P194" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q194" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R194" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S194" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="n">
+        <v>189.0</v>
+      </c>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C195" s="6" t="inlineStr">
+        <is>
+          <t>C25THB</t>
+        </is>
+      </c>
+      <c r="D195" s="7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E195" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F195" s="7" t="inlineStr">
+        <is>
+          <t>3502552641</t>
+        </is>
+      </c>
+      <c r="G195" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HB COFFEE</t>
+        </is>
+      </c>
+      <c r="H195" s="6" t="inlineStr">
+        <is>
+          <t>24 Huỳnh Văn Hớn, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I195" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J195" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K195" s="13" t="n">
+        <v>2657400.0</v>
+      </c>
+      <c r="L195" s="13" t="n">
+        <v>212592.0</v>
+      </c>
+      <c r="M195" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N195" s="13"/>
+      <c r="O195" s="13" t="n">
+        <v>2869992.0</v>
+      </c>
+      <c r="P195" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q195" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R195" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S195" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="n">
+        <v>190.0</v>
+      </c>
+      <c r="B196" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C196" s="6" t="inlineStr">
+        <is>
+          <t>C25THB</t>
+        </is>
+      </c>
+      <c r="D196" s="7" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E196" s="7" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="F196" s="7" t="inlineStr">
+        <is>
+          <t>3502552641</t>
+        </is>
+      </c>
+      <c r="G196" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HB COFFEE</t>
+        </is>
+      </c>
+      <c r="H196" s="6" t="inlineStr">
+        <is>
+          <t>24 Huỳnh Văn Hớn, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I196" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J196" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K196" s="13" t="n">
+        <v>4168970.0</v>
+      </c>
+      <c r="L196" s="13" t="n">
+        <v>333518.0</v>
+      </c>
+      <c r="M196" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N196" s="13"/>
+      <c r="O196" s="13" t="n">
+        <v>4502488.0</v>
+      </c>
+      <c r="P196" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q196" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R196" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S196" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="n">
+        <v>191.0</v>
+      </c>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>C25TVT</t>
+        </is>
+      </c>
+      <c r="D197" s="7" t="inlineStr">
+        <is>
+          <t>4353</t>
+        </is>
+      </c>
+      <c r="E197" s="7" t="inlineStr">
+        <is>
+          <t>09/12/2025</t>
+        </is>
+      </c>
+      <c r="F197" s="7" t="inlineStr">
+        <is>
+          <t>3700696229-003</t>
+        </is>
+      </c>
+      <c r="G197" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN THƯƠNG MẠI BIA SÀI GÒN MIỀN ĐÔNG TẠI BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H197" s="6" t="inlineStr">
+        <is>
+          <t>Số 6 Phan Đình Phùng, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I197" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J197" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THANH HƯƠNG BẾN ĐÌNH  - ĐIỂM BÁN C2 THÙY HƯƠNG</t>
+        </is>
+      </c>
+      <c r="K197" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L197" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M197" s="13"/>
+      <c r="N197" s="13"/>
+      <c r="O197" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P197" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q197" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R197" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S197" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>
